--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -5,22 +5,24 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123wq\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC3442E-B943-4047-A4D4-EF4C0306CF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3F1E9D-9121-4D77-B023-C4C8499A78A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
+    <sheet name="email" sheetId="2" r:id="rId2"/>
+    <sheet name="academic" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="263">
   <si>
     <t>Word</t>
   </si>
@@ -77,14 +79,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+    <t>content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>滿足的</t>
     </r>
     <r>
       <rPr>
@@ -93,16 +103,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>)田；實地</t>
+      <t>+with N / to v(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使滿足</t>
     </r>
     <r>
       <rPr>
@@ -111,6 +122,187 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> #contents(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>內容；內含物</t>
+    </r>
+  </si>
+  <si>
+    <t>intricate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>精密複雜的</t>
+    </r>
+  </si>
+  <si>
+    <t>intrinsic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本質的，根本的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(v)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>比起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>更喜歡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prefer A to B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手動的（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>WorryChefs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：手動刀）；體力的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>manual labor(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>操作手冊</t>
+    </r>
+  </si>
+  <si>
+    <t>in stock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>田；實地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>field trip</t>
     </r>
     <r>
@@ -143,18 +335,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(C)有機體（動植物、微生物等）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>有機體（動植物、微生物等）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>生物</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>鄰近</t>
     </r>
     <r>
       <rPr>
@@ -163,28 +384,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>)生物</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+      <t>+to</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（最能代表這個人事物的特性，跟</t>
     </r>
     <r>
       <rPr>
@@ -193,16 +406,46 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>UC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>)鄰近</t>
+      <t>fundamental</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的根本不同）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>在貨架上</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>不是</t>
     </r>
     <r>
       <rPr>
@@ -211,12 +454,415 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>+to</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>content</t>
+      <t>on</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aim at sth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>目標瞄準</t>
+    </r>
+  </si>
+  <si>
+    <t>hibernation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冬眠</t>
+    </r>
+  </si>
+  <si>
+    <t>vaccination program</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>include</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>involve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>疫苗接種計畫</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>包含</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>牽涉，需要</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>防災演習</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>practice a disaster drill</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disaster drill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bring sth to one's attention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>告訴某人某事</t>
+    </r>
+  </si>
+  <si>
+    <t>advise sb on sth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建議某人某事</t>
+    </r>
+  </si>
+  <si>
+    <t>request a brief extension on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請求延長時間</t>
+    </r>
+  </si>
+  <si>
+    <t>help sb out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>幫助某人脫離困境</t>
+    </r>
+  </si>
+  <si>
+    <t>on time = on schedule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>準時</t>
+    </r>
+  </si>
+  <si>
+    <t>workload = amount of work</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>工作量</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>因此不能講</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>number of workloads</t>
+    </r>
+  </si>
+  <si>
+    <t>on this team</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>隊伍中的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>不是用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60 percent of our grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分數</t>
+    </r>
+  </si>
+  <si>
+    <t>pass this course</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>通過課程</t>
+    </r>
+  </si>
+  <si>
+    <t>absence from sth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>缺席</t>
+    </r>
+  </si>
+  <si>
+    <t>take on a task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>承擔任務</t>
+    </r>
+  </si>
+  <si>
+    <t>customer service</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>客服</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>當作寫信對象要記得大寫</t>
+  </si>
+  <si>
+    <t>restart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>重開機</t>
+    </r>
+  </si>
+  <si>
+    <t>the exact same</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -231,7 +877,303 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>滿足的</t>
+      <t>一模一樣的</t>
+    </r>
+  </si>
+  <si>
+    <t>it is still in vain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>at no extra charge = at no additional cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>不另外收費</t>
+    </r>
+  </si>
+  <si>
+    <t>if it would be possible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如果可以的話</t>
+    </r>
+  </si>
+  <si>
+    <t>hope not to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)不希望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是do not hope to</t>
+  </si>
+  <si>
+    <t>make up for my absence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)為補償我的缺席</t>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>非常願意</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>would love to = be more than happy to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)抵達+at place</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>記得不是vt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scheduling conflict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UC)(C)時間衝到</t>
+  </si>
+  <si>
+    <t>seek = look for = search for</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)尋找</t>
+  </si>
+  <si>
+    <t>shared interest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)相同興趣</t>
+  </si>
+  <si>
+    <t>I would suggest you (should) v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I would like to provide a quick suggestion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(v)我想提供建議</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比I would like to give you suggestion文雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)建議</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>後面加原型動詞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比I would suggest you v還文雅，對事不對人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I would suggest ving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(v)我建議</t>
+  </si>
+  <si>
+    <t>It might be helpful to v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其實I suggest that還是太直接了；might又比could更客氣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am just a phone call away = You can call me on my regular number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)打給我</t>
+  </si>
+  <si>
+    <t>hardly = barely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)幾乎不</t>
+  </si>
+  <si>
+    <t>at once</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)同時</t>
+  </si>
+  <si>
+    <t>crowd flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)人流</t>
+  </si>
+  <si>
+    <t>leave smoothly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)流暢地離開</t>
+  </si>
+  <si>
+    <t>every part of N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)每一部分</t>
+  </si>
+  <si>
+    <t>less common</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)冷門的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>記得可以使用less來表示否定</t>
+  </si>
+  <si>
+    <t>read through these physical materials</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(v)讀完一遍實體書</t>
+  </si>
+  <si>
+    <t>push the deadline back by one week = extend the deadline by one week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)延長時間</t>
+  </si>
+  <si>
+    <t>annoying = disturbing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)煩人的</t>
+  </si>
+  <si>
+    <t>leave me exhausted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)讓我好累</t>
+  </si>
+  <si>
+    <t>the following day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>technician</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)技工</t>
+  </si>
+  <si>
+    <t>ensure = make sure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)確保</t>
+  </si>
+  <si>
+    <t>interesting = fascinating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)有趣的</t>
+  </si>
+  <si>
+    <t>the course counts toward the elective/required credits for my major</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)算入選修/必修分數</t>
+  </si>
+  <si>
+    <t>assignments = coursework = projects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UC)課堂作業</t>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>徒勞無功</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>不能只是寫</t>
     </r>
     <r>
       <rPr>
@@ -240,17 +1182,57 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>+with N / to v(vt)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>使滿足</t>
+      <t>but in vain</t>
+    </r>
+  </si>
+  <si>
+    <t>(C)隔天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前面不需要加介係詞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Word</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-being = welfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>福祉</t>
+    </r>
+  </si>
+  <si>
+    <t>prioritize A over B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>將</t>
     </r>
     <r>
       <rPr>
@@ -259,21 +1241,174 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> #contents(plural)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>內容；內含物</t>
-    </r>
-  </si>
-  <si>
-    <t>intricate</t>
+      <t>..</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>排在優先順位</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>health insurance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>健保</t>
+    </r>
+  </si>
+  <si>
+    <t>paid leave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有薪假</t>
+    </r>
+  </si>
+  <si>
+    <t>seek medical care</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>看醫生</t>
+    </r>
+  </si>
+  <si>
+    <t>medical expenses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>醫療開銷</t>
+    </r>
+  </si>
+  <si>
+    <t>company=firm=organization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>公司</t>
+    </r>
+  </si>
+  <si>
+    <t>A plays a far more important role than B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>重要多了</t>
+    </r>
+  </si>
+  <si>
+    <t>social strata = social hierarchy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>社會階級</t>
+    </r>
+  </si>
+  <si>
+    <t>rigid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -288,12 +1423,454 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>精密複雜的</t>
-    </r>
-  </si>
-  <si>
-    <t>intrinsic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+      <t>穩定的，不變的</t>
+    </r>
+  </si>
+  <si>
+    <t>academic achievements</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>成績好</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high school peer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>高中同學</t>
+    </r>
+  </si>
+  <si>
+    <t>high-paying position</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>高薪工作</t>
+    </r>
+  </si>
+  <si>
+    <t>influential figures = the class class</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上流階級</t>
+    </r>
+  </si>
+  <si>
+    <t>connection with = link with = tie to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有關係</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>可以搭配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>strong, established #relation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>比較強調私人關係</t>
+    </r>
+  </si>
+  <si>
+    <t>candidate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>候選人</t>
+    </r>
+  </si>
+  <si>
+    <t>traffic congestion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>交通堵塞</t>
+    </r>
+  </si>
+  <si>
+    <t>struggle with phone addiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手機成癮</t>
+    </r>
+  </si>
+  <si>
+    <t>stay focused on = concentrate on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>專注於</t>
+    </r>
+  </si>
+  <si>
+    <t>take a leisurely stroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>device = digital tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>master's program</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prepare me to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receive hands-on training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scarce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualified = suitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>competent(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>人具有實力的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personnel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the epidemic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>establish guidelines for</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>be born into poverty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>take the first step</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choose = opt for</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pursue higher education</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naturally rebellious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>act against</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participate in = join in = take part in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truly = fully = completely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firsthand = by oneself</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">expert + in/on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>學科</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciate = understand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>follow ethical guidelines</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>take higher priority than = be more important than</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infrastructure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolve = address</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metropolis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>悠閒散步</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>電子產品</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#electronics(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>電子產品</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>習得</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>碩士學位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>使我能夠</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>接受手把手的訓練</t>
+    </r>
   </si>
   <si>
     <r>
@@ -303,17 +1880,334 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>本質的，根本的</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>（最能代表這個人事物的特性，跟</t>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>數量稀少的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>夠資格的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#eligible(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>符合資格的，沒有比較級的用法</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>服務、產品具有競爭力的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(sing)(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>全體員工；人事部</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>用來表示新冠疫情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>建立綱領</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>生而貧窮</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#be born to poverty(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>天生適合貧窮</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>踏出第一步</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>選擇</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>深造</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>天生叛逆</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>反抗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>參與</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>完全</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>親自地</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>理解</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>遵守倫理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(sing)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>基礎建設</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>解決</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>大城市</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#metropolitan city</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>為冗餘說法</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>因此不能以</t>
     </r>
     <r>
       <rPr>
@@ -322,32 +2216,31 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>fundamental</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>的根本不同）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>(v)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>比起</t>
+      <t>the number of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>作為主詞</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)/'k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>ɑ</t>
     </r>
     <r>
       <rPr>
@@ -356,17 +2249,31 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>更喜歡</t>
+      <t>mpətənt/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>人具有實力的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>專家</t>
     </r>
     <r>
       <rPr>
@@ -375,20 +2282,282 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>A</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prefer A to B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+      <t xml:space="preserve">+in/on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>學科；專家</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+at ving/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>手做技能</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>更重要</t>
+    </r>
+  </si>
+  <si>
+    <t>the affluent = the rich</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有錢人</t>
+    </r>
+  </si>
+  <si>
+    <t>marginalized residents = the poor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>窮人</t>
+    </r>
+  </si>
+  <si>
+    <t>harmonious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>和睦的</t>
+    </r>
+  </si>
+  <si>
+    <t>neglected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>不被重視的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#supported(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>受重視的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gadgets = hardware</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>硬體東東</t>
+    </r>
+  </si>
+  <si>
+    <t>media = platforms = channels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>媒介，平台</t>
+    </r>
+  </si>
+  <si>
+    <t>be skilled at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>擅長</t>
+    </r>
+  </si>
+  <si>
+    <t>booth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>活動攤位</t>
+    </r>
+  </si>
+  <si>
+    <t>on that day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>那天</t>
+    </r>
+  </si>
+  <si>
+    <t>rely on commercial revenue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>仰賴收益</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -428,6 +2597,34 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -449,10 +2646,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -794,15 +2990,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -813,96 +3010,142 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -911,4 +3154,996 @@
     <ignoredError sqref="A1 B1 C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3F1E9D-9121-4D77-B023-C4C8499A78A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D20CDE-1389-4AB4-B8C4-D8E69D8AA034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="289">
   <si>
     <t>Word</t>
   </si>
@@ -1485,10 +1485,6 @@
     </r>
   </si>
   <si>
-    <t>influential figures = the class class</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(plural)</t>
     </r>
@@ -1719,10 +1715,6 @@
   </si>
   <si>
     <t>act against</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>participate in = join in = take part in</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2551,13 +2543,180 @@
       </rPr>
       <t>仰賴收益</t>
     </r>
+  </si>
+  <si>
+    <t>be tied up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>很忙，抽不開身</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>influential figures = the class class = elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appreciate = love</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)喜歡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>share</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)分享（比tell you客氣）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>go through</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)生效，被批准(vt)經歷苦難；仔細檢查；排練</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was wondering whether you could</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)我想知道您是否能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am wondering whether my submission failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)我想知道繳交是否失敗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)熱烈支持；迎接(adj)受歡迎的+sb/sth(UC)(C)歡迎give a warm welcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>people of diverse backgrounds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(plural)不同背景的人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>as someone new to sth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)身為新人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>required = mandatory = compulsory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>強制的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignite one's passion for</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>燃起興趣</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participate in = join in = take part in = engage in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regular weekday curriculum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(sing)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>課程安排</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-structured guidelines</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>良好制度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2624,6 +2783,12 @@
       <name val="細明體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2990,16 +3155,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3010,7 +3175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3018,7 +3183,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="16.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3029,7 +3194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="16.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3037,7 +3202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -3045,7 +3210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="16.2">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -3053,7 +3218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3061,7 +3226,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="16.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3072,7 +3237,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -3080,7 +3245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -3088,7 +3253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -3099,7 +3264,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -3107,7 +3272,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -3115,7 +3280,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="16.2">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -3123,7 +3288,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="16.2">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -3131,7 +3296,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="16.2">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -3139,12 +3304,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.6">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.6">
+      <c r="A22" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3158,14 +3331,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C63"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="38.75" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3176,7 +3349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
@@ -3185,7 +3358,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3194,7 +3367,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
@@ -3203,7 +3376,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -3212,12 +3385,12 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -3226,7 +3399,7 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -3237,7 +3410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>51</v>
       </c>
@@ -3248,7 +3421,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
@@ -3257,7 +3430,7 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>56</v>
       </c>
@@ -3266,7 +3439,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>58</v>
       </c>
@@ -3275,7 +3448,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
@@ -3284,12 +3457,12 @@
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>62</v>
       </c>
@@ -3300,7 +3473,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>65</v>
       </c>
@@ -3309,7 +3482,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
@@ -3318,7 +3491,7 @@
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>69</v>
       </c>
@@ -3329,7 +3502,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -3338,12 +3511,12 @@
       </c>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -3352,7 +3525,7 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
         <v>74</v>
       </c>
@@ -3363,7 +3536,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
         <v>77</v>
       </c>
@@ -3371,7 +3544,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
@@ -3379,7 +3552,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>81</v>
       </c>
@@ -3390,7 +3563,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -3398,10 +3571,10 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>86</v>
       </c>
@@ -3409,7 +3582,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>88</v>
       </c>
@@ -3417,7 +3590,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -3428,7 +3601,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>91</v>
       </c>
@@ -3439,7 +3612,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -3450,7 +3623,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
@@ -3461,7 +3634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>101</v>
       </c>
@@ -3469,10 +3642,10 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>103</v>
       </c>
@@ -3480,7 +3653,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>105</v>
       </c>
@@ -3488,7 +3661,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>107</v>
       </c>
@@ -3496,7 +3669,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>109</v>
       </c>
@@ -3504,7 +3677,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>111</v>
       </c>
@@ -3512,10 +3685,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>113</v>
       </c>
@@ -3526,7 +3699,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>116</v>
       </c>
@@ -3534,7 +3707,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>118</v>
       </c>
@@ -3542,10 +3715,10 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>120</v>
       </c>
@@ -3553,7 +3726,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>122</v>
       </c>
@@ -3561,7 +3734,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>124</v>
       </c>
@@ -3572,7 +3745,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="2" t="s">
         <v>125</v>
       </c>
@@ -3580,10 +3753,10 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="1"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
         <v>127</v>
       </c>
@@ -3591,7 +3764,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
         <v>129</v>
       </c>
@@ -3599,7 +3772,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
         <v>131</v>
       </c>
@@ -3607,12 +3780,76 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B54" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B58" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B59" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B60" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B62" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B63" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3623,15 +3860,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
@@ -3642,7 +3879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16.2">
       <c r="A2" s="1" t="s">
         <v>140</v>
       </c>
@@ -3650,7 +3887,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="16.2">
       <c r="A3" s="2" t="s">
         <v>142</v>
       </c>
@@ -3658,7 +3895,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="16.2">
       <c r="A4" s="2" t="s">
         <v>144</v>
       </c>
@@ -3666,7 +3903,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="2" t="s">
         <v>146</v>
       </c>
@@ -3674,7 +3911,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="16.2">
       <c r="A6" s="2" t="s">
         <v>148</v>
       </c>
@@ -3682,7 +3919,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="16.2">
       <c r="A7" s="1" t="s">
         <v>150</v>
       </c>
@@ -3690,7 +3927,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
         <v>152</v>
       </c>
@@ -3698,10 +3935,10 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
         <v>154</v>
       </c>
@@ -3709,7 +3946,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="16.2">
       <c r="A11" s="2" t="s">
         <v>156</v>
       </c>
@@ -3717,7 +3954,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
@@ -3725,7 +3962,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="2" t="s">
         <v>160</v>
       </c>
@@ -3733,7 +3970,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="16.2">
       <c r="A14" s="2" t="s">
         <v>162</v>
       </c>
@@ -3741,7 +3978,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
         <v>164</v>
       </c>
@@ -3749,397 +3986,429 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="16.2">
+      <c r="A17" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="16.2">
+      <c r="A18" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" ht="16.2">
+      <c r="A20" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="16.2">
+      <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="16.2">
+      <c r="A22" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="16.2">
+      <c r="A23" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16.2">
+      <c r="A24" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" ht="16.2">
+      <c r="A26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C24" s="1" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="16.2">
+      <c r="A27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="1" t="s">
+    <row r="28" spans="1:3" ht="16.2">
+      <c r="A28" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="1:3" ht="16.2">
+      <c r="A29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="30" spans="1:3" ht="16.2">
+      <c r="A30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.2">
+      <c r="A31" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="32" spans="1:3" ht="16.2">
+      <c r="A32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.2">
+      <c r="A33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16.2">
+      <c r="A34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16.2">
+      <c r="A35" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16.2">
+      <c r="A36" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" ht="16.2">
+      <c r="A38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16.2">
+      <c r="A39" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16.2">
+      <c r="A40" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16.2">
+      <c r="A41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16.2">
+      <c r="A42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="16.2">
+      <c r="A43" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" ht="16.2">
+      <c r="A45" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16.2">
+      <c r="A46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.2">
+      <c r="A47" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.2">
+      <c r="A48" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="1" t="s">
+    <row r="49" spans="1:3" ht="16.2">
+      <c r="A49" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.2">
+      <c r="A50" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.2">
+      <c r="A52" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-    </row>
-    <row r="45" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B48" s="1" t="s">
+    <row r="53" spans="1:3" ht="16.2">
+      <c r="A53" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.2">
+      <c r="A54" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="16.2">
+      <c r="A55" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.2">
+      <c r="A56" s="1" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="57" spans="1:3" ht="16.2">
+      <c r="A57" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="58" spans="1:3" ht="16.2">
+      <c r="A58" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="59" spans="1:3" ht="16.2">
+      <c r="A59" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B59" s="1" t="s">
+    </row>
+    <row r="60" spans="1:3" ht="16.2">
+      <c r="A60" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="62" spans="1:3" ht="16.2">
+      <c r="A62" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:3" ht="16.2">
+      <c r="A63" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="64" spans="1:3" ht="16.2">
+      <c r="A64" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:2" ht="16.2">
+      <c r="A65" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:2" ht="16.2">
+      <c r="A66" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>262</v>
+    <row r="68" spans="1:2" ht="15.6">
+      <c r="A68" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.6">
+      <c r="A69" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.6">
+      <c r="A70" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.6">
+      <c r="A71" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D20CDE-1389-4AB4-B8C4-D8E69D8AA034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C81896-AD9C-44D0-8EA3-F4C6E91BB7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="323">
   <si>
     <t>Word</t>
   </si>
@@ -1332,10 +1332,6 @@
     </r>
   </si>
   <si>
-    <t>company=firm=organization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(C)</t>
     </r>
@@ -1663,22 +1659,6 @@
   </si>
   <si>
     <t>competitive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>competent(adj)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>人具有實力的</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2564,10 +2544,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>influential figures = the class class = elite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>appreciate = love</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2708,6 +2684,339 @@
         <family val="2"/>
       </rPr>
       <t>良好制度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>influential figures = the upper class = elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>company = firm = organization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precipitate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>促成；使急速下墜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(vt)(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>沉澱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(UC)(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>沉澱物</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>percipitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>降雨；急躁；沉澱反應</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>my experience was unfortunately a bit disappointing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)你推薦這什麼爛店的好聽說法</t>
+  </si>
+  <si>
+    <t>not as good as I had expected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)沒想像中那麼好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>felt let down = felt disappointed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)感到失望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>issue = problem = challenge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I probably won't head back here</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)不會再來了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anytime soon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)短期內</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)自助餐餐廳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>try out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)嘗試+方法/店家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>累死了</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>培養嗜好</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burned out = worn out = exhausted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>make it a hobby to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immediate environments/surroudings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>現況</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exercise = workouts = regular physical activity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>運動</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boost one's mood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>心情好</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer a healthy mental escape from dailt pressures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使逃離日常壓力</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mental health is a self-regulated state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>心裡健康是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>自我調節的</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2779,16 +3088,16 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="細明體"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3155,7 +3464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
@@ -3314,10 +3623,26 @@
     </row>
     <row r="22" spans="1:2" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.2">
+      <c r="A23" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.6">
+      <c r="A24" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3331,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="38.77734375" customWidth="1"/>
@@ -3790,66 +4115,130 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B60" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B61" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B62" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s">
-        <v>274</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B65" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B66" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B67" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B68" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B70" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B71" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B72" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3860,7 +4249,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -3929,10 +4318,10 @@
     </row>
     <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3940,77 +4329,77 @@
     </row>
     <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.2">
       <c r="A11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.2">
       <c r="A14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="2" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.2">
       <c r="A17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.2">
       <c r="A18" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4018,45 +4407,45 @@
     </row>
     <row r="20" spans="1:3" ht="16.2">
       <c r="A20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.2">
       <c r="A21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.2">
       <c r="A22" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.2">
       <c r="A23" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.2">
       <c r="A24" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4064,96 +4453,96 @@
     </row>
     <row r="26" spans="1:3" ht="16.2">
       <c r="A26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16.2">
       <c r="A27" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16.2">
       <c r="A28" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16.2">
       <c r="A29" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.2">
       <c r="A30" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.2">
       <c r="A31" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16.2">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.2">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>288</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16.2">
       <c r="A34" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16.2">
       <c r="A35" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16.2">
       <c r="A36" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4161,53 +4550,53 @@
     </row>
     <row r="38" spans="1:3" ht="16.2">
       <c r="A38" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.2">
       <c r="A39" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16.2">
       <c r="A40" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.2">
       <c r="A41" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.2">
       <c r="A42" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16.2">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4215,200 +4604,256 @@
     </row>
     <row r="45" spans="1:3" ht="16.2">
       <c r="A45" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16.2">
       <c r="A46" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16.2">
       <c r="A47" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16.2">
       <c r="A48" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.2">
       <c r="A49" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16.2">
       <c r="A50" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16.2">
       <c r="A52" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16.2">
       <c r="A53" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16.2">
       <c r="A54" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16.2">
       <c r="A55" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16.2">
       <c r="A56" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16.2">
       <c r="A57" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.2">
       <c r="A58" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16.2">
       <c r="A59" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16.2">
       <c r="A60" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.2">
       <c r="A62" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.2">
       <c r="A63" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.2">
       <c r="A64" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16.2">
       <c r="A65" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="16.2">
       <c r="A66" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.6">
+      <c r="A73" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.6">
+      <c r="A74" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.6">
+      <c r="A75" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.6">
+      <c r="A76" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.6">
+      <c r="A77" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.6">
+      <c r="A78" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.6">
+      <c r="A79" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C81896-AD9C-44D0-8EA3-F4C6E91BB7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2182A068-6327-4382-AB66-4737C6139682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="390">
   <si>
     <t>Word</t>
   </si>
@@ -801,10 +801,6 @@
     </r>
   </si>
   <si>
-    <t>take on a task</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(vt)</t>
     </r>
@@ -1087,10 +1083,6 @@
   </si>
   <si>
     <t>記得可以使用less來表示否定</t>
-  </si>
-  <si>
-    <t>read through these physical materials</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>(v)讀完一遍實體書</t>
@@ -1726,10 +1718,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>follow ethical guidelines</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>take higher priority than = be more important than</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3017,6 +3005,758 @@
         <charset val="136"/>
       </rPr>
       <t>自我調節的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>市集攤位</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stall = stand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banquet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>宴會</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pastry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>糕點</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>茶點</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expedited shipping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>急件服務</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># expedite(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>促進，加快</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>facility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amenity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>生活福利設施</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>public amenities</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># basic amenities(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>基礎生活設施</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>render</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsolete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>過時的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>特定場所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sports facility(UC)(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>產品功能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>speech recognition facility</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>才能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+for sth</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>render me speechless</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；翻譯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>render the book into A from B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；提供表演</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>服務</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upcoming</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)即將發生的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>In parituclar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)特別是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dining option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)用餐選擇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overcrowded tourist trap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)騙觀光客的地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)公共場所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internet café = cybercafe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)網咖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I find the story to be interesting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>我發現這個故事很有趣</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># find</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>跟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>make</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>不同，不能直接加上補語</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>individuals = ordinary citizens = residents</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>人</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>read through these physical materials = digest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>follow ethical guidelines/standards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>讓人放鬆的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>氣氛、面容、地方、人的存在；沉穩的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>remain serene, lead a serene life</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I hope everything is going well with you</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)你最近好嗎（等一下要爆噴）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I hope you are having a wonderful week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)你最近好嗎（等一下要求他）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)確認進度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>so far</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)到目前為止（用於說明現在進度）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproduce the experiment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)重現實驗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>take on a task = take charge of a task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarely have the time to v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>很少有時間可以</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoughtful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>精密設計的；體貼的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>沉思的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>convey = promote = impart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>宣傳知識</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waste separation = recycling = sorting bottles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>做回收</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diligent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>認真的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>not an inevitable outcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>可避免的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adhere to = follow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>遵守</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journalistic integrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新聞倫理</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(conj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>只要</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provided that = as long as = so long as</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>given the fact that</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(conj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>考慮到</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3464,12 +4204,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3484,7 +4224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.2">
+    <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3492,7 +4232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.2">
+    <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3503,7 +4243,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.2">
+    <row r="4" spans="1:3" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3511,7 +4251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.2">
+    <row r="5" spans="1:3" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -3519,7 +4259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.2">
+    <row r="7" spans="1:3" ht="16.5">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -3527,7 +4267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.2">
+    <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3535,7 +4275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.2">
+    <row r="9" spans="1:3" ht="16.5">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3546,7 +4286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.2">
+    <row r="10" spans="1:3" ht="16.5">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -3554,7 +4294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.2">
+    <row r="12" spans="1:3" ht="16.5">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -3562,7 +4302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.2">
+    <row r="13" spans="1:3" ht="16.5">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -3573,7 +4313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.2">
+    <row r="15" spans="1:3" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -3581,7 +4321,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.2">
+    <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -3589,7 +4329,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.2">
+    <row r="17" spans="1:3" ht="16.5">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -3597,7 +4337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.2">
+    <row r="18" spans="1:3" ht="16.5">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -3605,7 +4345,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.2">
+    <row r="19" spans="1:3" ht="16.5">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -3613,7 +4353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.6">
+    <row r="21" spans="1:3" ht="15.75">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,28 +4361,109 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.6">
+    <row r="22" spans="1:3" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="16.2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75">
+      <c r="A24" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.6">
-      <c r="A24" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>292</v>
+    </row>
+    <row r="26" spans="1:3" ht="15.75">
+      <c r="A26" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75">
+      <c r="A27" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75">
+      <c r="A28" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75">
+      <c r="A30" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.5">
+      <c r="A31" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75">
+      <c r="A32" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.5">
+      <c r="A33" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75">
+      <c r="A34" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75">
+      <c r="A36" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -3656,11 +4477,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:C85"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3775,10 +4596,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C13" s="1"/>
     </row>
@@ -3789,50 +4610,50 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C19" s="1"/>
     </row>
@@ -3843,57 +4664,57 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
         <v>74</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
         <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3901,70 +4722,70 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
         <v>86</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
         <v>88</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
         <v>101</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3972,42 +4793,42 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
         <v>103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
         <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" t="s">
         <v>109</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
         <v>111</v>
-      </c>
-      <c r="B40" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4015,29 +4836,29 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
         <v>113</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4045,37 +4866,37 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -4083,162 +4904,250 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B66" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B67" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B70" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B71" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B72" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B74" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B75" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B76" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B78" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B79" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B81" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B82" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B83" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B85" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -4249,17 +5158,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4268,592 +5177,688 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.2">
+    <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5">
+      <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.2">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" ht="16.5">
+      <c r="A4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.2">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:3" ht="16.5">
+      <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.2">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:3" ht="16.5">
+      <c r="A6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.2">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:3" ht="16.5">
+      <c r="A7" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.2">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:3" ht="16.5">
+      <c r="A8" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="16.2">
-      <c r="A8" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="16.2">
+    <row r="10" spans="1:3" ht="16.5">
       <c r="A10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5">
+      <c r="A11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.2">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:3" ht="16.5">
+      <c r="A12" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.2">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:3" ht="16.5">
+      <c r="A13" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.2">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:3" ht="16.5">
+      <c r="A14" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.2">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:3" ht="16.5">
+      <c r="A15" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.2">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:3" ht="16.5">
+      <c r="A16" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="16.5">
+      <c r="A17" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.2">
-      <c r="A16" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.2">
-      <c r="A17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="16.5">
+      <c r="A18" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="16.2">
-      <c r="A18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="16.2">
+    <row r="20" spans="1:3" ht="16.5">
       <c r="A20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.5">
+      <c r="A21" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16.2">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:3" ht="16.5">
+      <c r="A22" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16.2">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:3" ht="16.5">
+      <c r="A23" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16.5">
+      <c r="A24" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="16.2">
-      <c r="A23" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="16.2">
-      <c r="A24" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="16.2">
+    <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16.5">
+      <c r="A27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16.5">
+      <c r="A28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16.5">
+      <c r="A29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.2">
-      <c r="A27" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="30" spans="1:3" ht="16.5">
+      <c r="A30" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="16.2">
-      <c r="A28" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.5">
+      <c r="A31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="16.2">
-      <c r="A29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16.2">
-      <c r="A30" s="2" t="s">
+    <row r="32" spans="1:3" ht="16.5">
+      <c r="A32" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="16.2">
-      <c r="A31" s="2" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="16.5">
+      <c r="A33" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16.5">
+      <c r="A34" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C31" s="1" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="16.5">
+      <c r="A35" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16.2">
-      <c r="A32" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="1" t="s">
+    <row r="36" spans="1:3" ht="16.5">
+      <c r="A36" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="16.2">
-      <c r="A33" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="16.2">
-      <c r="A34" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.2">
-      <c r="A35" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="16.2">
-      <c r="A36" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="16.2">
+    <row r="38" spans="1:3" ht="16.5">
       <c r="A38" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16.5">
+      <c r="A39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16.5">
+      <c r="A40" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C38" s="1" t="s">
+    </row>
+    <row r="41" spans="1:3" ht="16.5">
+      <c r="A41" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16.2">
-      <c r="A39" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B39" s="1" t="s">
+    <row r="42" spans="1:3" ht="16.5">
+      <c r="A42" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16.2">
-      <c r="A40" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B40" s="1" t="s">
+    <row r="43" spans="1:3" ht="16.5">
+      <c r="A43" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="16.2">
-      <c r="A41" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="16.2">
-      <c r="A42" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="16.2">
-      <c r="A43" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:3" ht="16.2">
+    <row r="45" spans="1:3" ht="16.5">
       <c r="A45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16.5">
+      <c r="A46" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.5">
+      <c r="A47" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.5">
+      <c r="A48" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.5">
+      <c r="A49" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.5">
+      <c r="A50" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5">
+      <c r="A52" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5">
+      <c r="A53" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.5">
+      <c r="A54" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="16.5">
+      <c r="A55" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.5">
+      <c r="A56" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="16.5">
+      <c r="A57" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.5">
+      <c r="A58" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="16.5">
+      <c r="A59" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="16.5">
+      <c r="A60" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.5">
+      <c r="A62" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.5">
+      <c r="A63" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="16.5">
+      <c r="A64" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.5">
+      <c r="A65" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.5">
+      <c r="A66" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75">
+      <c r="A68" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75">
+      <c r="A69" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75">
+      <c r="A70" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75">
+      <c r="A71" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="16.2">
-      <c r="A46" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="16.2">
-      <c r="A47" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="16.2">
-      <c r="A48" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="16.2">
-      <c r="A49" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="16.2">
-      <c r="A50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="16.2">
-      <c r="A52" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="16.2">
-      <c r="A53" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="16.2">
-      <c r="A54" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="16.2">
-      <c r="A55" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="16.2">
-      <c r="A56" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="16.2">
-      <c r="A57" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="16.2">
-      <c r="A58" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="16.2">
-      <c r="A59" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="16.2">
-      <c r="A60" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="16.2">
-      <c r="A62" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="16.2">
-      <c r="A63" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="16.2">
-      <c r="A64" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="16.2">
-      <c r="A65" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="16.2">
-      <c r="A66" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="15.6">
-      <c r="A68" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="15.6">
-      <c r="A69" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.6">
-      <c r="A70" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.6">
-      <c r="A71" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="15.6">
-      <c r="A73" s="1" t="s">
+    </row>
+    <row r="72" spans="1:2" ht="15.75">
+      <c r="A72" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75">
+      <c r="A74" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75">
+      <c r="A75" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B73" s="1" t="s">
+    </row>
+    <row r="76" spans="1:2" ht="15.75">
+      <c r="A76" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75">
+      <c r="A77" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75">
+      <c r="A78" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" ht="15.6">
-      <c r="A74" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="15.6">
-      <c r="A75" s="1" t="s">
+    </row>
+    <row r="79" spans="1:2" ht="15.75">
+      <c r="A79" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="15.6">
-      <c r="A76" s="1" t="s">
+    </row>
+    <row r="80" spans="1:2" ht="15.75">
+      <c r="A80" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="15.6">
-      <c r="A77" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="15.6">
-      <c r="A78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="15.6">
-      <c r="A79" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>316</v>
+    </row>
+    <row r="82" spans="1:2" ht="15.75">
+      <c r="A82" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15.75">
+      <c r="A83" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="16.5">
+      <c r="A84" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75">
+      <c r="A85" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15.75">
+      <c r="A86" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.75">
+      <c r="A87" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15.75">
+      <c r="A88" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75">
+      <c r="A89" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75">
+      <c r="A90" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.75">
+      <c r="A91" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.75">
+      <c r="A92" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2182A068-6327-4382-AB66-4737C6139682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFF346E-2F97-4158-8793-06B61FFC2038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3702,7 +3702,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>journalistic integrity</t>
+    <r>
+      <t>(conj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>只要</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provided that = as long as = so long as</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>given the fact that</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(conj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>考慮到</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rasearch/journalistic integrity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3715,48 +3754,18 @@
         <color theme="1"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
+      </rPr>
+      <t>研究/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
         <charset val="136"/>
       </rPr>
       <t>新聞倫理</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(conj)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>只要</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>provided that = as long as = so long as</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>given the fact that</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(conj)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>考慮到</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5839,26 +5848,26 @@
     </row>
     <row r="90" spans="1:2" ht="15.75">
       <c r="A90" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="15.75">
       <c r="A91" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="15.75">
       <c r="A92" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFF346E-2F97-4158-8793-06B61FFC2038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8F2FF6-CEC3-4CDD-B690-80DD4B8E0F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="421">
   <si>
     <t>Word</t>
   </si>
@@ -3766,6 +3766,332 @@
         <charset val="136"/>
       </rPr>
       <t>新聞倫理</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impact = affect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>影響</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hormone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>費洛蒙</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was hoping we could</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)我想要更禮貌的講法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host a fair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)舉辦活動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heartfelt connection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)情感連結</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enduring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>持久的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>喜好</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foster passion for sth in sb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>慢慢激發感情</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># ignite, inspire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>有相同文法，但是強調「瞬間、爆發」</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>standard dress shirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>一般男用正式襯衫</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>只</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>only, just</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>好多了</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseline expectation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>基本要求</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rival</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>競爭對手</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the others</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>更好</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>edge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>優勢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+over sb in sth</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saturated market</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>紅海</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4213,12 +4539,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4233,7 +4559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5">
+    <row r="2" spans="1:3" ht="16.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -4241,7 +4567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5">
+    <row r="3" spans="1:3" ht="16.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4252,7 +4578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5">
+    <row r="4" spans="1:3" ht="16.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4260,7 +4586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5">
+    <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -4268,7 +4594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5">
+    <row r="7" spans="1:3" ht="16.2">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -4276,7 +4602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5">
+    <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4284,7 +4610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.5">
+    <row r="9" spans="1:3" ht="16.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4295,7 +4621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.5">
+    <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -4303,7 +4629,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5">
+    <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -4311,7 +4637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5">
+    <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -4322,7 +4648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.5">
+    <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -4330,7 +4656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5">
+    <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -4338,7 +4664,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.5">
+    <row r="17" spans="1:3" ht="16.2">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -4346,7 +4672,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.5">
+    <row r="18" spans="1:3" ht="16.2">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -4354,7 +4680,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16.5">
+    <row r="19" spans="1:3" ht="16.2">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -4362,7 +4688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75">
+    <row r="21" spans="1:3" ht="15.6">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -4370,7 +4696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75">
+    <row r="22" spans="1:3" ht="15.6">
       <c r="A22" s="1" t="s">
         <v>256</v>
       </c>
@@ -4378,7 +4704,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16.5">
+    <row r="23" spans="1:3" ht="16.2">
       <c r="A23" s="1" t="s">
         <v>286</v>
       </c>
@@ -4386,7 +4712,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75">
+    <row r="24" spans="1:3" ht="15.6">
       <c r="A24" s="1" t="s">
         <v>288</v>
       </c>
@@ -4394,7 +4720,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75">
+    <row r="26" spans="1:3" ht="15.6">
       <c r="A26" s="1" t="s">
         <v>321</v>
       </c>
@@ -4402,7 +4728,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75">
+    <row r="27" spans="1:3" ht="15.6">
       <c r="A27" s="1" t="s">
         <v>322</v>
       </c>
@@ -4410,7 +4736,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75">
+    <row r="28" spans="1:3" ht="15.6">
       <c r="A28" s="1" t="s">
         <v>324</v>
       </c>
@@ -4418,7 +4744,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75">
+    <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
         <v>326</v>
       </c>
@@ -4429,7 +4755,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.5">
+    <row r="31" spans="1:3" ht="16.2">
       <c r="A31" s="1" t="s">
         <v>329</v>
       </c>
@@ -4437,7 +4763,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75">
+    <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
         <v>330</v>
       </c>
@@ -4448,7 +4774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16.5">
+    <row r="33" spans="1:3" ht="16.2">
       <c r="A33" s="1" t="s">
         <v>333</v>
       </c>
@@ -4456,7 +4782,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75">
+    <row r="34" spans="1:3" ht="15.6">
       <c r="A34" s="1" t="s">
         <v>334</v>
       </c>
@@ -4464,7 +4790,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75">
+    <row r="36" spans="1:3" ht="15.6">
       <c r="A36" s="1" t="s">
         <v>350</v>
       </c>
@@ -4473,6 +4799,22 @@
       </c>
       <c r="C36" s="1" t="s">
         <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.6">
+      <c r="A37" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.6">
+      <c r="A38" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4486,11 +4828,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:C89"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="38.75" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5157,6 +5499,30 @@
       </c>
       <c r="B85" t="s">
         <v>368</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B87" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B88" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B89" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -5167,11 +5533,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5186,7 +5552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5">
+    <row r="2" spans="1:3" ht="16.2">
       <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
@@ -5194,7 +5560,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5">
+    <row r="3" spans="1:3" ht="16.2">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -5202,7 +5568,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5">
+    <row r="4" spans="1:3" ht="16.2">
       <c r="A4" s="2" t="s">
         <v>142</v>
       </c>
@@ -5210,7 +5576,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5">
+    <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
@@ -5218,7 +5584,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5">
+    <row r="6" spans="1:3" ht="16.2">
       <c r="A6" s="2" t="s">
         <v>146</v>
       </c>
@@ -5226,7 +5592,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5">
+    <row r="7" spans="1:3" ht="16.2">
       <c r="A7" s="1" t="s">
         <v>148</v>
       </c>
@@ -5234,7 +5600,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5">
+    <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
         <v>284</v>
       </c>
@@ -5245,7 +5611,7 @@
     <row r="9" spans="1:3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="16.5">
+    <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
         <v>151</v>
       </c>
@@ -5253,7 +5619,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5">
+    <row r="11" spans="1:3" ht="16.2">
       <c r="A11" s="2" t="s">
         <v>153</v>
       </c>
@@ -5261,7 +5627,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5">
+    <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="2" t="s">
         <v>155</v>
       </c>
@@ -5269,7 +5635,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5">
+    <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="2" t="s">
         <v>157</v>
       </c>
@@ -5277,7 +5643,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.5">
+    <row r="14" spans="1:3" ht="16.2">
       <c r="A14" s="2" t="s">
         <v>159</v>
       </c>
@@ -5285,7 +5651,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.5">
+    <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
         <v>161</v>
       </c>
@@ -5293,7 +5659,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5">
+    <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="2" t="s">
         <v>283</v>
       </c>
@@ -5301,7 +5667,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.5">
+    <row r="17" spans="1:3" ht="16.2">
       <c r="A17" s="2" t="s">
         <v>164</v>
       </c>
@@ -5312,7 +5678,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.5">
+    <row r="18" spans="1:3" ht="16.2">
       <c r="A18" s="2" t="s">
         <v>167</v>
       </c>
@@ -5323,7 +5689,7 @@
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="16.5">
+    <row r="20" spans="1:3" ht="16.2">
       <c r="A20" s="2" t="s">
         <v>169</v>
       </c>
@@ -5331,7 +5697,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16.5">
+    <row r="21" spans="1:3" ht="16.2">
       <c r="A21" s="1" t="s">
         <v>171</v>
       </c>
@@ -5339,7 +5705,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16.5">
+    <row r="22" spans="1:3" ht="16.2">
       <c r="A22" s="2" t="s">
         <v>173</v>
       </c>
@@ -5347,7 +5713,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16.5">
+    <row r="23" spans="1:3" ht="16.2">
       <c r="A23" s="2" t="s">
         <v>175</v>
       </c>
@@ -5355,7 +5721,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16.5">
+    <row r="24" spans="1:3" ht="16.2">
       <c r="A24" s="2" t="s">
         <v>176</v>
       </c>
@@ -5369,7 +5735,7 @@
     <row r="25" spans="1:3">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="16.5">
+    <row r="26" spans="1:3" ht="16.2">
       <c r="A26" s="2" t="s">
         <v>177</v>
       </c>
@@ -5377,7 +5743,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.5">
+    <row r="27" spans="1:3" ht="16.2">
       <c r="A27" s="2" t="s">
         <v>178</v>
       </c>
@@ -5385,7 +5751,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16.5">
+    <row r="28" spans="1:3" ht="16.2">
       <c r="A28" s="1" t="s">
         <v>179</v>
       </c>
@@ -5393,7 +5759,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16.5">
+    <row r="29" spans="1:3" ht="16.2">
       <c r="A29" s="2" t="s">
         <v>180</v>
       </c>
@@ -5401,7 +5767,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16.5">
+    <row r="30" spans="1:3" ht="16.2">
       <c r="A30" s="2" t="s">
         <v>181</v>
       </c>
@@ -5412,7 +5778,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.5">
+    <row r="31" spans="1:3" ht="16.2">
       <c r="A31" s="2" t="s">
         <v>182</v>
       </c>
@@ -5423,7 +5789,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16.5">
+    <row r="32" spans="1:3" ht="16.2">
       <c r="A32" s="2" t="s">
         <v>183</v>
       </c>
@@ -5431,7 +5797,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16.5">
+    <row r="33" spans="1:3" ht="16.2">
       <c r="A33" s="2" t="s">
         <v>285</v>
       </c>
@@ -5439,7 +5805,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.5">
+    <row r="34" spans="1:3" ht="16.2">
       <c r="A34" s="2" t="s">
         <v>184</v>
       </c>
@@ -5447,7 +5813,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16.5">
+    <row r="35" spans="1:3" ht="16.2">
       <c r="A35" s="2" t="s">
         <v>185</v>
       </c>
@@ -5455,7 +5821,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16.5">
+    <row r="36" spans="1:3" ht="16.2">
       <c r="A36" s="2" t="s">
         <v>186</v>
       </c>
@@ -5466,7 +5832,7 @@
     <row r="37" spans="1:3">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="16.5">
+    <row r="38" spans="1:3" ht="16.2">
       <c r="A38" s="2" t="s">
         <v>187</v>
       </c>
@@ -5477,7 +5843,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16.5">
+    <row r="39" spans="1:3" ht="16.2">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -5485,7 +5851,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16.5">
+    <row r="40" spans="1:3" ht="16.2">
       <c r="A40" s="2" t="s">
         <v>189</v>
       </c>
@@ -5493,7 +5859,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16.5">
+    <row r="41" spans="1:3" ht="16.2">
       <c r="A41" s="2" t="s">
         <v>190</v>
       </c>
@@ -5501,7 +5867,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="16.5">
+    <row r="42" spans="1:3" ht="16.2">
       <c r="A42" s="2" t="s">
         <v>191</v>
       </c>
@@ -5509,7 +5875,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16.5">
+    <row r="43" spans="1:3" ht="16.2">
       <c r="A43" s="1" t="s">
         <v>192</v>
       </c>
@@ -5520,7 +5886,7 @@
     <row r="44" spans="1:3">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:3" ht="16.5">
+    <row r="45" spans="1:3" ht="16.2">
       <c r="A45" s="2" t="s">
         <v>278</v>
       </c>
@@ -5528,7 +5894,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16.5">
+    <row r="46" spans="1:3" ht="16.2">
       <c r="A46" s="2" t="s">
         <v>193</v>
       </c>
@@ -5536,7 +5902,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16.5">
+    <row r="47" spans="1:3" ht="16.2">
       <c r="A47" s="1" t="s">
         <v>194</v>
       </c>
@@ -5544,7 +5910,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16.5">
+    <row r="48" spans="1:3" ht="16.2">
       <c r="A48" s="2" t="s">
         <v>195</v>
       </c>
@@ -5552,7 +5918,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16.5">
+    <row r="49" spans="1:3" ht="16.2">
       <c r="A49" s="2" t="s">
         <v>196</v>
       </c>
@@ -5560,7 +5926,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16.5">
+    <row r="50" spans="1:3" ht="16.2">
       <c r="A50" s="2" t="s">
         <v>356</v>
       </c>
@@ -5568,7 +5934,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16.5">
+    <row r="52" spans="1:3" ht="16.2">
       <c r="A52" s="2" t="s">
         <v>197</v>
       </c>
@@ -5576,7 +5942,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16.5">
+    <row r="53" spans="1:3" ht="16.2">
       <c r="A53" s="2" t="s">
         <v>198</v>
       </c>
@@ -5584,7 +5950,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16.5">
+    <row r="54" spans="1:3" ht="16.2">
       <c r="A54" s="2" t="s">
         <v>199</v>
       </c>
@@ -5592,7 +5958,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16.5">
+    <row r="55" spans="1:3" ht="16.2">
       <c r="A55" s="2" t="s">
         <v>200</v>
       </c>
@@ -5603,7 +5969,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16.5">
+    <row r="56" spans="1:3" ht="16.2">
       <c r="A56" s="1" t="s">
         <v>235</v>
       </c>
@@ -5611,7 +5977,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16.5">
+    <row r="57" spans="1:3" ht="16.2">
       <c r="A57" s="1" t="s">
         <v>237</v>
       </c>
@@ -5619,7 +5985,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16.5">
+    <row r="58" spans="1:3" ht="16.2">
       <c r="A58" s="1" t="s">
         <v>239</v>
       </c>
@@ -5627,7 +5993,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16.5">
+    <row r="59" spans="1:3" ht="16.2">
       <c r="A59" s="1" t="s">
         <v>241</v>
       </c>
@@ -5638,7 +6004,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16.5">
+    <row r="60" spans="1:3" ht="16.2">
       <c r="A60" s="1" t="s">
         <v>244</v>
       </c>
@@ -5646,7 +6012,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16.5">
+    <row r="62" spans="1:3" ht="16.2">
       <c r="A62" s="1" t="s">
         <v>246</v>
       </c>
@@ -5654,7 +6020,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16.5">
+    <row r="63" spans="1:3" ht="16.2">
       <c r="A63" s="1" t="s">
         <v>248</v>
       </c>
@@ -5662,7 +6028,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16.5">
+    <row r="64" spans="1:3" ht="16.2">
       <c r="A64" s="1" t="s">
         <v>250</v>
       </c>
@@ -5670,7 +6036,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.5">
+    <row r="65" spans="1:2" ht="16.2">
       <c r="A65" s="1" t="s">
         <v>252</v>
       </c>
@@ -5678,7 +6044,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.5">
+    <row r="66" spans="1:2" ht="16.2">
       <c r="A66" s="1" t="s">
         <v>254</v>
       </c>
@@ -5686,7 +6052,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75">
+    <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
         <v>274</v>
       </c>
@@ -5694,7 +6060,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75">
+    <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="1" t="s">
         <v>276</v>
       </c>
@@ -5702,7 +6068,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75">
+    <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="1" t="s">
         <v>279</v>
       </c>
@@ -5710,7 +6076,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75">
+    <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="1" t="s">
         <v>281</v>
       </c>
@@ -5718,7 +6084,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75">
+    <row r="72" spans="1:2" ht="15.6">
       <c r="A72" s="1" t="s">
         <v>357</v>
       </c>
@@ -5726,7 +6092,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75">
+    <row r="74" spans="1:2" ht="15.6">
       <c r="A74" s="1" t="s">
         <v>314</v>
       </c>
@@ -5734,7 +6100,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75">
+    <row r="75" spans="1:2" ht="15.6">
       <c r="A75" s="1" t="s">
         <v>316</v>
       </c>
@@ -5742,7 +6108,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75">
+    <row r="76" spans="1:2" ht="15.6">
       <c r="A76" s="1" t="s">
         <v>308</v>
       </c>
@@ -5750,7 +6116,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75">
+    <row r="77" spans="1:2" ht="15.6">
       <c r="A77" s="1" t="s">
         <v>309</v>
       </c>
@@ -5758,7 +6124,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75">
+    <row r="78" spans="1:2" ht="15.6">
       <c r="A78" s="1" t="s">
         <v>318</v>
       </c>
@@ -5766,7 +6132,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75">
+    <row r="79" spans="1:2" ht="15.6">
       <c r="A79" s="1" t="s">
         <v>310</v>
       </c>
@@ -5774,7 +6140,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75">
+    <row r="80" spans="1:2" ht="15.6">
       <c r="A80" s="1" t="s">
         <v>312</v>
       </c>
@@ -5782,7 +6148,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75">
+    <row r="82" spans="1:3" ht="15.6">
       <c r="A82" s="1" t="s">
         <v>353</v>
       </c>
@@ -5790,7 +6156,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75">
+    <row r="83" spans="1:3" ht="15.6">
       <c r="A83" s="1" t="s">
         <v>370</v>
       </c>
@@ -5798,7 +6164,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16.5">
+    <row r="84" spans="1:3" ht="16.2">
       <c r="A84" s="1" t="s">
         <v>372</v>
       </c>
@@ -5806,7 +6172,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75">
+    <row r="85" spans="1:3" ht="15.6">
       <c r="A85" s="1" t="s">
         <v>374</v>
       </c>
@@ -5814,7 +6180,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75">
+    <row r="86" spans="1:3" ht="15.6">
       <c r="A86" s="1" t="s">
         <v>376</v>
       </c>
@@ -5822,7 +6188,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75">
+    <row r="87" spans="1:3" ht="15.6">
       <c r="A87" s="1" t="s">
         <v>378</v>
       </c>
@@ -5830,7 +6196,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75">
+    <row r="88" spans="1:3" ht="15.6">
       <c r="A88" s="1" t="s">
         <v>380</v>
       </c>
@@ -5838,7 +6204,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75">
+    <row r="89" spans="1:3" ht="15.6">
       <c r="A89" s="1" t="s">
         <v>382</v>
       </c>
@@ -5846,7 +6212,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75">
+    <row r="90" spans="1:3" ht="15.6">
       <c r="A90" s="1" t="s">
         <v>388</v>
       </c>
@@ -5854,7 +6220,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75">
+    <row r="91" spans="1:3" ht="15.6">
       <c r="A91" s="1" t="s">
         <v>385</v>
       </c>
@@ -5862,12 +6228,93 @@
         <v>384</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75">
+    <row r="92" spans="1:3" ht="15.6">
       <c r="A92" s="1" t="s">
         <v>386</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15.6">
+      <c r="A94" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15.6">
+      <c r="A95" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15.6">
+      <c r="A96" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15.6">
+      <c r="A97" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15.6">
+      <c r="A98" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15.6">
+      <c r="A99" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15.6">
+      <c r="A100" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15.6">
+      <c r="A101" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.6">
+      <c r="A102" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8F2FF6-CEC3-4CDD-B690-80DD4B8E0F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87380382-8548-46A9-9FB0-C6DEE4361F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
     <sheet name="email" sheetId="2" r:id="rId2"/>
-    <sheet name="academic" sheetId="4" r:id="rId3"/>
+    <sheet name="有禮貌專區" sheetId="5" r:id="rId3"/>
+    <sheet name="academic" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="447">
   <si>
     <t>Word</t>
   </si>
@@ -900,10 +901,6 @@
     </r>
   </si>
   <si>
-    <t>if it would be possible</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(idiom)</t>
     </r>
@@ -1001,10 +998,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比I would like to give you suggestion文雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(idiom)建議</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1013,10 +1006,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比I would suggest you v還文雅，對事不對人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>I would suggest ving</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1025,10 +1014,6 @@
   </si>
   <si>
     <t>It might be helpful to v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其實I suggest that還是太直接了；might又比could更客氣</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4092,6 +4077,296 @@
         <family val="2"/>
       </rPr>
       <t>紅海</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>視覺的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>可看到的；顯眼的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>draft the report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)起草報告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respond to messages</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)回覆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if it would/might be possible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was wondering if you might be able to offer some guidance or help us address this situation.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(idiom)可以幫忙嗎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 寫給長輩不能要求他怎麼幫忙，只能問他能不能幫忙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 比I would like to give you suggestion文雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 比I would suggest you v還文雅，對事不對人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 其實I suggest that還是太直接了；might又比could更客氣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vulnerable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>脆弱的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consumer = customer = patron = buyer = purchaser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>買家</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploitative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>剝削的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterfeit / branded</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>冒牌的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>正牌的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swallow the financial loss helplessly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無助地吞下經濟損失</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profit margin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cut corners</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>切西瓜</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>利潤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>可能是非法的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># commercial revenue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>合法的</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4539,7 +4814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
@@ -4698,123 +4973,139 @@
     </row>
     <row r="22" spans="1:3" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.2">
       <c r="A23" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.2">
       <c r="A31" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.2">
       <c r="A33" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.6">
       <c r="A34" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.6">
       <c r="A36" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.6">
       <c r="A37" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.6">
       <c r="A38" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.6">
+      <c r="A39" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.6">
+      <c r="A40" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4828,7 +5119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="38.77734375" customWidth="1"/>
@@ -4947,7 +5238,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>60</v>
@@ -4993,10 +5284,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5015,201 +5306,189 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>82</v>
-      </c>
+      <c r="A25" s="1"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="1"/>
+      <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
+      <c r="A30" s="2"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
-      </c>
+      <c r="A36" s="1"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
+      <c r="A40" s="1"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1"/>
+      <c r="A41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>355</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5217,312 +5496,234 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
-      </c>
-      <c r="C48" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="1"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>127</v>
+        <v>256</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>129</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B57" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B60" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="B61" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B62" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B63" t="s">
-        <v>268</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B64" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="B65" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="B67" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="B68" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="B69" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B70" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="B71" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="B72" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B74" t="s">
-        <v>339</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B73" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="B75" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2" t="s">
-        <v>342</v>
+        <v>392</v>
       </c>
       <c r="B76" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2" t="s">
-        <v>344</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B78" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2" t="s">
-        <v>348</v>
+        <v>421</v>
       </c>
       <c r="B79" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B81" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B82" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B83" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B85" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B87" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B88" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B89" t="s">
-        <v>399</v>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B80" t="s">
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5532,8 +5733,150 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EDC9FC-1DB6-4BC4-96F7-C5677C1DF68D}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B18" t="s">
+        <v>427</v>
+      </c>
+      <c r="C18" t="s">
+        <v>428</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -5543,7 +5886,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5554,58 +5897,58 @@
     </row>
     <row r="2" spans="1:3" ht="16.2">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.2">
       <c r="A3" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.2">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.2">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16.2">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.2">
       <c r="A8" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5613,77 +5956,77 @@
     </row>
     <row r="10" spans="1:3" ht="16.2">
       <c r="A10" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.2">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.2">
       <c r="A12" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.2">
       <c r="A13" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.2">
       <c r="A14" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.2">
       <c r="A15" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.2">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.2">
       <c r="A17" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.2">
       <c r="A18" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5691,45 +6034,45 @@
     </row>
     <row r="20" spans="1:3" ht="16.2">
       <c r="A20" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.2">
       <c r="A21" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.2">
       <c r="A22" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.2">
       <c r="A23" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.2">
       <c r="A24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5737,96 +6080,96 @@
     </row>
     <row r="26" spans="1:3" ht="16.2">
       <c r="A26" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16.2">
       <c r="A27" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16.2">
       <c r="A28" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16.2">
       <c r="A29" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.2">
       <c r="A30" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.2">
       <c r="A31" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16.2">
       <c r="A32" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.2">
       <c r="A33" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16.2">
       <c r="A34" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16.2">
       <c r="A35" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16.2">
       <c r="A36" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -5834,53 +6177,53 @@
     </row>
     <row r="38" spans="1:3" ht="16.2">
       <c r="A38" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.2">
       <c r="A39" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16.2">
       <c r="A40" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.2">
       <c r="A41" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.2">
       <c r="A42" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16.2">
       <c r="A43" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5888,433 +6231,492 @@
     </row>
     <row r="45" spans="1:3" ht="16.2">
       <c r="A45" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16.2">
       <c r="A46" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16.2">
       <c r="A47" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16.2">
       <c r="A48" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.2">
       <c r="A49" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16.2">
       <c r="A50" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16.2">
       <c r="A52" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16.2">
       <c r="A53" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16.2">
       <c r="A54" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16.2">
       <c r="A55" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16.2">
       <c r="A56" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16.2">
       <c r="A57" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.2">
       <c r="A58" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16.2">
       <c r="A59" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16.2">
       <c r="A60" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.2">
       <c r="A62" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.2">
       <c r="A63" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.2">
       <c r="A64" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16.2">
       <c r="A65" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="16.2">
       <c r="A66" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.6">
       <c r="A72" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15.6">
       <c r="A74" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15.6">
       <c r="A75" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.6">
       <c r="A76" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.6">
       <c r="A77" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.6">
       <c r="A78" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.6">
       <c r="A79" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.6">
       <c r="A80" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.6">
       <c r="A82" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.6">
       <c r="A83" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.2">
       <c r="A84" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.6">
       <c r="A85" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.6">
       <c r="A86" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.6">
       <c r="A87" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.6">
       <c r="A88" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.6">
       <c r="A89" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.6">
       <c r="A90" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.6">
       <c r="A91" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.6">
       <c r="A92" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.6">
       <c r="A94" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.6">
       <c r="A95" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.6">
       <c r="A96" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.6">
       <c r="A97" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.6">
       <c r="A98" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.6">
       <c r="A99" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.6">
       <c r="A100" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.6">
       <c r="A101" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.6">
       <c r="A102" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15.6">
+      <c r="A104" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.6">
+      <c r="A105" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15.6">
+      <c r="A106" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.6">
+      <c r="A107" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15.6">
+      <c r="A108" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="16.2">
+      <c r="A109" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15.6">
+      <c r="A110" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87380382-8548-46A9-9FB0-C6DEE4361F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21490C57-EA00-4AEF-A175-59A7D513CE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="467">
   <si>
     <t>Word</t>
   </si>
@@ -3510,10 +3510,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(vi)確認進度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>so far</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4367,6 +4363,198 @@
         <family val="2"/>
       </rPr>
       <t>合法的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)確認近況（查勤或者擔心）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weight training sessions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)重訓課</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step away from research</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)從研究抽身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># distract不會用在負面的事情上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>develop anxiety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>感到焦慮</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># depression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>已經是心理疾病了</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seek psychological counseling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># seek medical care</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>進行心理諮商</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardly/barely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>幾乎不</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>盡量少用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>來表示否定</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>交流</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stay in touch with intimate friends = contact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exert a negative impact on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>對…造成負面影響</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nurture bond with</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>培養感情</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4817,9 +5005,9 @@
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4834,7 +5022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.2">
+    <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -4842,7 +5030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.2">
+    <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4853,7 +5041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.2">
+    <row r="4" spans="1:3" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4861,7 +5049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.2">
+    <row r="5" spans="1:3" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -4869,7 +5057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.2">
+    <row r="7" spans="1:3" ht="16.5">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -4877,7 +5065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.2">
+    <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4885,7 +5073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.2">
+    <row r="9" spans="1:3" ht="16.5">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4896,7 +5084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.2">
+    <row r="10" spans="1:3" ht="16.5">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -4904,7 +5092,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.2">
+    <row r="12" spans="1:3" ht="16.5">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -4912,7 +5100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.2">
+    <row r="13" spans="1:3" ht="16.5">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -4923,7 +5111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.2">
+    <row r="15" spans="1:3" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -4931,7 +5119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.2">
+    <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -4939,7 +5127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.2">
+    <row r="17" spans="1:3" ht="16.5">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -4947,7 +5135,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.2">
+    <row r="18" spans="1:3" ht="16.5">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -4955,7 +5143,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16.2">
+    <row r="19" spans="1:3" ht="16.5">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -4963,7 +5151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6">
+    <row r="21" spans="1:3" ht="15.75">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -4971,7 +5159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6">
+    <row r="22" spans="1:3" ht="15.75">
       <c r="A22" s="1" t="s">
         <v>252</v>
       </c>
@@ -4979,7 +5167,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16.2">
+    <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="1" t="s">
         <v>282</v>
       </c>
@@ -4987,7 +5175,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6">
+    <row r="24" spans="1:3" ht="15.75">
       <c r="A24" s="1" t="s">
         <v>284</v>
       </c>
@@ -4995,7 +5183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.6">
+    <row r="26" spans="1:3" ht="15.75">
       <c r="A26" s="1" t="s">
         <v>317</v>
       </c>
@@ -5003,7 +5191,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6">
+    <row r="27" spans="1:3" ht="15.75">
       <c r="A27" s="1" t="s">
         <v>318</v>
       </c>
@@ -5011,7 +5199,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6">
+    <row r="28" spans="1:3" ht="15.75">
       <c r="A28" s="1" t="s">
         <v>320</v>
       </c>
@@ -5019,7 +5207,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.6">
+    <row r="30" spans="1:3" ht="15.75">
       <c r="A30" s="1" t="s">
         <v>322</v>
       </c>
@@ -5030,7 +5218,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.2">
+    <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="1" t="s">
         <v>325</v>
       </c>
@@ -5038,7 +5226,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6">
+    <row r="32" spans="1:3" ht="15.75">
       <c r="A32" s="1" t="s">
         <v>326</v>
       </c>
@@ -5049,7 +5237,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16.2">
+    <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="1" t="s">
         <v>329</v>
       </c>
@@ -5057,7 +5245,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6">
+    <row r="34" spans="1:3" ht="15.75">
       <c r="A34" s="1" t="s">
         <v>330</v>
       </c>
@@ -5065,7 +5253,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6">
+    <row r="36" spans="1:3" ht="15.75">
       <c r="A36" s="1" t="s">
         <v>346</v>
       </c>
@@ -5076,36 +5264,36 @@
         <v>348</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6">
+    <row r="37" spans="1:3" ht="15.75">
       <c r="A37" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:3" ht="15.75">
+      <c r="A38" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.6">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.6">
+    </row>
+    <row r="39" spans="1:3" ht="15.75">
       <c r="A39" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B39" s="1" t="s">
+    </row>
+    <row r="40" spans="1:3" ht="15.75">
+      <c r="A40" s="1" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.6">
-      <c r="A40" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5119,11 +5307,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5238,7 +5426,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>60</v>
@@ -5667,63 +5855,82 @@
         <v>359</v>
       </c>
       <c r="B71" t="s">
-        <v>360</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B72" t="s">
         <v>361</v>
-      </c>
-      <c r="B72" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B73" t="s">
         <v>363</v>
-      </c>
-      <c r="B73" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B75" t="s">
         <v>390</v>
-      </c>
-      <c r="B75" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B76" t="s">
         <v>392</v>
-      </c>
-      <c r="B76" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B77" t="s">
         <v>394</v>
-      </c>
-      <c r="B77" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B79" t="s">
         <v>421</v>
-      </c>
-      <c r="B79" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B80" t="s">
         <v>423</v>
       </c>
-      <c r="B80" t="s">
-        <v>424</v>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B82" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B83" t="s">
+        <v>450</v>
+      </c>
+      <c r="C83" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -5735,10 +5942,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EDC9FC-1DB6-4BC4-96F7-C5677C1DF68D}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="41.33203125" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+    <col min="1" max="1" width="41.375" customWidth="1"/>
+    <col min="2" max="2" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5754,7 +5961,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>71</v>
@@ -5776,7 +5983,7 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5787,7 +5994,7 @@
         <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5798,7 +6005,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5859,13 +6066,13 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B18" t="s">
         <v>426</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>427</v>
-      </c>
-      <c r="C18" t="s">
-        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -5876,11 +6083,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5895,7 +6102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.2">
+    <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>134</v>
       </c>
@@ -5903,7 +6110,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.2">
+    <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="2" t="s">
         <v>136</v>
       </c>
@@ -5911,7 +6118,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.2">
+    <row r="4" spans="1:3" ht="16.5">
       <c r="A4" s="2" t="s">
         <v>138</v>
       </c>
@@ -5919,7 +6126,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.2">
+    <row r="5" spans="1:3" ht="16.5">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -5927,7 +6134,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.2">
+    <row r="6" spans="1:3" ht="16.5">
       <c r="A6" s="2" t="s">
         <v>142</v>
       </c>
@@ -5935,7 +6142,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.2">
+    <row r="7" spans="1:3" ht="16.5">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -5943,7 +6150,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.2">
+    <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="2" t="s">
         <v>280</v>
       </c>
@@ -5954,7 +6161,7 @@
     <row r="9" spans="1:3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="16.2">
+    <row r="10" spans="1:3" ht="16.5">
       <c r="A10" s="2" t="s">
         <v>147</v>
       </c>
@@ -5962,7 +6169,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.2">
+    <row r="11" spans="1:3" ht="16.5">
       <c r="A11" s="2" t="s">
         <v>149</v>
       </c>
@@ -5970,7 +6177,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.2">
+    <row r="12" spans="1:3" ht="16.5">
       <c r="A12" s="2" t="s">
         <v>151</v>
       </c>
@@ -5978,7 +6185,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.2">
+    <row r="13" spans="1:3" ht="16.5">
       <c r="A13" s="2" t="s">
         <v>153</v>
       </c>
@@ -5986,7 +6193,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.2">
+    <row r="14" spans="1:3" ht="16.5">
       <c r="A14" s="2" t="s">
         <v>155</v>
       </c>
@@ -5994,7 +6201,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.2">
+    <row r="15" spans="1:3" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>157</v>
       </c>
@@ -6002,7 +6209,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.2">
+    <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="2" t="s">
         <v>279</v>
       </c>
@@ -6010,7 +6217,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.2">
+    <row r="17" spans="1:3" ht="16.5">
       <c r="A17" s="2" t="s">
         <v>160</v>
       </c>
@@ -6021,7 +6228,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.2">
+    <row r="18" spans="1:3" ht="16.5">
       <c r="A18" s="2" t="s">
         <v>163</v>
       </c>
@@ -6032,7 +6239,7 @@
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="16.2">
+    <row r="20" spans="1:3" ht="16.5">
       <c r="A20" s="2" t="s">
         <v>165</v>
       </c>
@@ -6040,7 +6247,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16.2">
+    <row r="21" spans="1:3" ht="16.5">
       <c r="A21" s="1" t="s">
         <v>167</v>
       </c>
@@ -6048,7 +6255,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16.2">
+    <row r="22" spans="1:3" ht="16.5">
       <c r="A22" s="2" t="s">
         <v>169</v>
       </c>
@@ -6056,7 +6263,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16.2">
+    <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="2" t="s">
         <v>171</v>
       </c>
@@ -6064,7 +6271,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16.2">
+    <row r="24" spans="1:3" ht="16.5">
       <c r="A24" s="2" t="s">
         <v>172</v>
       </c>
@@ -6078,7 +6285,7 @@
     <row r="25" spans="1:3">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="16.2">
+    <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="2" t="s">
         <v>173</v>
       </c>
@@ -6086,7 +6293,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.2">
+    <row r="27" spans="1:3" ht="16.5">
       <c r="A27" s="2" t="s">
         <v>174</v>
       </c>
@@ -6094,7 +6301,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16.2">
+    <row r="28" spans="1:3" ht="16.5">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -6102,7 +6309,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16.2">
+    <row r="29" spans="1:3" ht="16.5">
       <c r="A29" s="2" t="s">
         <v>176</v>
       </c>
@@ -6110,7 +6317,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16.2">
+    <row r="30" spans="1:3" ht="16.5">
       <c r="A30" s="2" t="s">
         <v>177</v>
       </c>
@@ -6121,7 +6328,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.2">
+    <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="2" t="s">
         <v>178</v>
       </c>
@@ -6132,7 +6339,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16.2">
+    <row r="32" spans="1:3" ht="16.5">
       <c r="A32" s="2" t="s">
         <v>179</v>
       </c>
@@ -6140,7 +6347,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16.2">
+    <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="2" t="s">
         <v>281</v>
       </c>
@@ -6148,7 +6355,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.2">
+    <row r="34" spans="1:3" ht="16.5">
       <c r="A34" s="2" t="s">
         <v>180</v>
       </c>
@@ -6156,7 +6363,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16.2">
+    <row r="35" spans="1:3" ht="16.5">
       <c r="A35" s="2" t="s">
         <v>181</v>
       </c>
@@ -6164,7 +6371,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16.2">
+    <row r="36" spans="1:3" ht="16.5">
       <c r="A36" s="2" t="s">
         <v>182</v>
       </c>
@@ -6175,7 +6382,7 @@
     <row r="37" spans="1:3">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="16.2">
+    <row r="38" spans="1:3" ht="16.5">
       <c r="A38" s="2" t="s">
         <v>183</v>
       </c>
@@ -6186,7 +6393,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16.2">
+    <row r="39" spans="1:3" ht="16.5">
       <c r="A39" s="2" t="s">
         <v>184</v>
       </c>
@@ -6194,7 +6401,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16.2">
+    <row r="40" spans="1:3" ht="16.5">
       <c r="A40" s="2" t="s">
         <v>185</v>
       </c>
@@ -6202,7 +6409,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16.2">
+    <row r="41" spans="1:3" ht="16.5">
       <c r="A41" s="2" t="s">
         <v>186</v>
       </c>
@@ -6210,7 +6417,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="16.2">
+    <row r="42" spans="1:3" ht="16.5">
       <c r="A42" s="2" t="s">
         <v>187</v>
       </c>
@@ -6218,7 +6425,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16.2">
+    <row r="43" spans="1:3" ht="16.5">
       <c r="A43" s="1" t="s">
         <v>188</v>
       </c>
@@ -6229,7 +6436,7 @@
     <row r="44" spans="1:3">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:3" ht="16.2">
+    <row r="45" spans="1:3" ht="16.5">
       <c r="A45" s="2" t="s">
         <v>274</v>
       </c>
@@ -6237,7 +6444,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16.2">
+    <row r="46" spans="1:3" ht="16.5">
       <c r="A46" s="2" t="s">
         <v>189</v>
       </c>
@@ -6245,7 +6452,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16.2">
+    <row r="47" spans="1:3" ht="16.5">
       <c r="A47" s="1" t="s">
         <v>190</v>
       </c>
@@ -6253,7 +6460,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16.2">
+    <row r="48" spans="1:3" ht="16.5">
       <c r="A48" s="2" t="s">
         <v>191</v>
       </c>
@@ -6261,7 +6468,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16.2">
+    <row r="49" spans="1:3" ht="16.5">
       <c r="A49" s="2" t="s">
         <v>192</v>
       </c>
@@ -6269,7 +6476,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16.2">
+    <row r="50" spans="1:3" ht="16.5">
       <c r="A50" s="2" t="s">
         <v>352</v>
       </c>
@@ -6277,7 +6484,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16.2">
+    <row r="52" spans="1:3" ht="16.5">
       <c r="A52" s="2" t="s">
         <v>193</v>
       </c>
@@ -6285,7 +6492,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16.2">
+    <row r="53" spans="1:3" ht="16.5">
       <c r="A53" s="2" t="s">
         <v>194</v>
       </c>
@@ -6293,7 +6500,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16.2">
+    <row r="54" spans="1:3" ht="16.5">
       <c r="A54" s="2" t="s">
         <v>195</v>
       </c>
@@ -6301,7 +6508,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16.2">
+    <row r="55" spans="1:3" ht="16.5">
       <c r="A55" s="2" t="s">
         <v>196</v>
       </c>
@@ -6312,7 +6519,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16.2">
+    <row r="56" spans="1:3" ht="16.5">
       <c r="A56" s="1" t="s">
         <v>231</v>
       </c>
@@ -6320,7 +6527,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16.2">
+    <row r="57" spans="1:3" ht="16.5">
       <c r="A57" s="1" t="s">
         <v>233</v>
       </c>
@@ -6328,7 +6535,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16.2">
+    <row r="58" spans="1:3" ht="16.5">
       <c r="A58" s="1" t="s">
         <v>235</v>
       </c>
@@ -6336,7 +6543,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16.2">
+    <row r="59" spans="1:3" ht="16.5">
       <c r="A59" s="1" t="s">
         <v>237</v>
       </c>
@@ -6347,7 +6554,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16.2">
+    <row r="60" spans="1:3" ht="16.5">
       <c r="A60" s="1" t="s">
         <v>240</v>
       </c>
@@ -6355,7 +6562,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16.2">
+    <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="1" t="s">
         <v>242</v>
       </c>
@@ -6363,7 +6570,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16.2">
+    <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="1" t="s">
         <v>244</v>
       </c>
@@ -6371,7 +6578,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16.2">
+    <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="1" t="s">
         <v>246</v>
       </c>
@@ -6379,7 +6586,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.2">
+    <row r="65" spans="1:2" ht="16.5">
       <c r="A65" s="1" t="s">
         <v>248</v>
       </c>
@@ -6387,7 +6594,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.2">
+    <row r="66" spans="1:2" ht="16.5">
       <c r="A66" s="1" t="s">
         <v>250</v>
       </c>
@@ -6395,7 +6602,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.6">
+    <row r="68" spans="1:2" ht="15.75">
       <c r="A68" s="1" t="s">
         <v>270</v>
       </c>
@@ -6403,7 +6610,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.6">
+    <row r="69" spans="1:2" ht="15.75">
       <c r="A69" s="1" t="s">
         <v>272</v>
       </c>
@@ -6411,7 +6618,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.6">
+    <row r="70" spans="1:2" ht="15.75">
       <c r="A70" s="1" t="s">
         <v>275</v>
       </c>
@@ -6419,7 +6626,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.6">
+    <row r="71" spans="1:2" ht="15.75">
       <c r="A71" s="1" t="s">
         <v>277</v>
       </c>
@@ -6427,7 +6634,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.6">
+    <row r="72" spans="1:2" ht="15.75">
       <c r="A72" s="1" t="s">
         <v>353</v>
       </c>
@@ -6435,7 +6642,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.6">
+    <row r="74" spans="1:2" ht="15.75">
       <c r="A74" s="1" t="s">
         <v>310</v>
       </c>
@@ -6443,7 +6650,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.6">
+    <row r="75" spans="1:2" ht="15.75">
       <c r="A75" s="1" t="s">
         <v>312</v>
       </c>
@@ -6451,7 +6658,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.6">
+    <row r="76" spans="1:2" ht="15.75">
       <c r="A76" s="1" t="s">
         <v>304</v>
       </c>
@@ -6459,7 +6666,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.6">
+    <row r="77" spans="1:2" ht="15.75">
       <c r="A77" s="1" t="s">
         <v>305</v>
       </c>
@@ -6467,7 +6674,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.6">
+    <row r="78" spans="1:2" ht="15.75">
       <c r="A78" s="1" t="s">
         <v>314</v>
       </c>
@@ -6475,7 +6682,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.6">
+    <row r="79" spans="1:2" ht="15.75">
       <c r="A79" s="1" t="s">
         <v>306</v>
       </c>
@@ -6483,7 +6690,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.6">
+    <row r="80" spans="1:2" ht="15.75">
       <c r="A80" s="1" t="s">
         <v>308</v>
       </c>
@@ -6491,7 +6698,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.6">
+    <row r="82" spans="1:3" ht="15.75">
       <c r="A82" s="1" t="s">
         <v>349</v>
       </c>
@@ -6499,224 +6706,281 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.6">
+    <row r="83" spans="1:3" ht="15.75">
       <c r="A83" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B83" s="1" t="s">
+    </row>
+    <row r="84" spans="1:3" ht="16.5">
+      <c r="A84" s="1" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="16.2">
-      <c r="A84" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B84" s="1" t="s">
+    </row>
+    <row r="85" spans="1:3" ht="15.75">
+      <c r="A85" s="1" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="15.6">
-      <c r="A85" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:3" ht="15.75">
+      <c r="A86" s="1" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="15.6">
-      <c r="A86" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B86" s="1" t="s">
+    </row>
+    <row r="87" spans="1:3" ht="15.75">
+      <c r="A87" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="15.6">
-      <c r="A87" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B87" s="1" t="s">
+    </row>
+    <row r="88" spans="1:3" ht="15.75">
+      <c r="A88" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="15.6">
-      <c r="A88" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B88" s="1" t="s">
+    </row>
+    <row r="89" spans="1:3" ht="15.75">
+      <c r="A89" s="1" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="15.6">
-      <c r="A89" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B89" s="1" t="s">
+    </row>
+    <row r="90" spans="1:3" ht="15.75">
+      <c r="A90" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15.75">
+      <c r="A91" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.6">
-      <c r="A90" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="15.6">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:3" ht="15.75">
+      <c r="A92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="15.6">
-      <c r="A92" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="15.6">
+    </row>
+    <row r="94" spans="1:3" ht="15.75">
       <c r="A94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:3" ht="15.75">
+      <c r="A95" s="1" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="15.6">
-      <c r="A95" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B95" s="1" t="s">
+    </row>
+    <row r="96" spans="1:3" ht="15.75">
+      <c r="A96" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="15.6">
-      <c r="A96" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C96" s="1" t="s">
+    </row>
+    <row r="97" spans="1:3" ht="15.75">
+      <c r="A97" s="1" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="15.6">
-      <c r="A97" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B97" s="1" t="s">
+    </row>
+    <row r="98" spans="1:3" ht="15.75">
+      <c r="A98" s="1" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.6">
-      <c r="A98" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C98" s="1" t="s">
+    </row>
+    <row r="99" spans="1:3" ht="15.75">
+      <c r="A99" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.6">
-      <c r="A99" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B99" s="1" t="s">
+    </row>
+    <row r="100" spans="1:3" ht="15.75">
+      <c r="A100" s="1" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.6">
-      <c r="A100" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C100" s="1" t="s">
+    </row>
+    <row r="101" spans="1:3" ht="15.75">
+      <c r="A101" s="1" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.6">
-      <c r="A101" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B101" s="1" t="s">
+    </row>
+    <row r="102" spans="1:3" ht="15.75">
+      <c r="A102" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.6">
-      <c r="A102" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="15.6">
+    </row>
+    <row r="104" spans="1:3" ht="15.75">
       <c r="A104" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B104" s="1" t="s">
+    </row>
+    <row r="105" spans="1:3" ht="15.75">
+      <c r="A105" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.6">
-      <c r="A105" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B105" s="1" t="s">
+    </row>
+    <row r="106" spans="1:3" ht="15.75">
+      <c r="A106" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="15.6">
-      <c r="A106" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B106" s="1" t="s">
+    </row>
+    <row r="107" spans="1:3" ht="15.75">
+      <c r="A107" s="1" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="15.6">
-      <c r="A107" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B107" s="1" t="s">
+    </row>
+    <row r="108" spans="1:3" ht="15.75">
+      <c r="A108" s="1" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="15.6">
-      <c r="A108" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B108" s="1" t="s">
+    </row>
+    <row r="109" spans="1:3" ht="16.5">
+      <c r="A109" s="1" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="16.2">
-      <c r="A109" s="1" t="s">
+      <c r="B109" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15.75">
+      <c r="A110" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="15.6">
-      <c r="A110" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>444</v>
+    </row>
+    <row r="112" spans="1:3" ht="15.75">
+      <c r="A112" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15.75">
+      <c r="A113" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15.75">
+      <c r="A114" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="15.75">
+      <c r="A115" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15.75">
+      <c r="A116" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="15.75">
+      <c r="A117" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21490C57-EA00-4AEF-A175-59A7D513CE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60B7AA-CD24-493F-997A-CC594F03F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="541">
   <si>
     <t>Word</t>
   </si>
@@ -1565,10 +1565,6 @@
     </r>
   </si>
   <si>
-    <t>struggle with phone addiction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(vi)</t>
     </r>
@@ -1611,10 +1607,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>acquire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>master's program</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1711,10 +1703,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>resolve = address</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>metropolis</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2878,10 +2866,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>immediate environments/surroudings</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(C)</t>
     </r>
@@ -2945,10 +2929,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>offer a healthy mental escape from dailt pressures</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(vt)</t>
     </r>
@@ -3722,10 +3702,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rasearch/journalistic integrity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(UC)</t>
     </r>
@@ -4120,10 +4096,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(vi)起草報告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>respond to messages</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4449,10 +4421,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hardly/barely</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>(adv)</t>
     </r>
@@ -4469,6 +4437,114 @@
   </si>
   <si>
     <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>交流</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stay in touch with intimate friends = contact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exert a negative impact on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>對…造成負面影響</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nurture bond with</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>培養感情</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>research/journalistic integrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer a healthy mental escape from daily pressures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immediate environments / surroudings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspiring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年輕有為的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>be efficient at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>做…有效率</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve"># </t>
     </r>
     <r>
@@ -4493,6 +4569,25 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cannot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -4501,6 +4596,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>struggle immensely with phone addiction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>(vi)</t>
     </r>
@@ -4511,16 +4610,403 @@
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>交流</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stay in touch with intimate friends = contact</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>exert a negative impact on</t>
+      <t>努力做</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>很少</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarely = seldom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>沒有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hardly = barely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>那麼否定</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Had it not been for N, I would have</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>要是沒有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>我就會（假設語氣）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolve = address = tackle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foster genuine mastery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>人真正融會貫通</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquire = absorb = assimilate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knowledge = insight = principle = idea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>知識</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit substantial effort / onself to ving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)起草報告（有禮貌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># draft表示我有初步想法，還需要對方再琢磨一番，因此有禮貌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>this position require a four-hour shift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)這工作要求每天工作四小時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submit paper to another conference held four months from now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)從ISSCC改投VLSI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>these/those/their</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(pron)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>都是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>開頭的五字代名詞</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>長期且不畏艱難地奮鬥</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># strive-strove-striven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj)幾乎不可能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 不要太絕對時可以用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>virtually / nearly impossible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>access online academic resources</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)使用線上學術資源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">request that S + (should) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>原</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>v</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 記得S是物品才有禮貌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggressive regime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>好戰政體</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diplomatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>外交的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competing interests</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>利益衝突</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negotiate consensus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>透過協商達成共識</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naturally = inherently</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>本質地</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sustain = preserve = maintain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4534,28 +5020,161 @@
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>對…造成負面影響</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nurture bond with</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(vt)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>培養感情</t>
-    </r>
+      <t>保持</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multilateral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>多國之間的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># diplomacy(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>外交</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t># consensus negotiation(UC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>達成共識</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>an issue with sth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)sth有問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># 使用with而非in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wake up energized</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)早上起來精神煥發</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stamina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UC)體力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># energized強調有某個事物使你精神變好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gesture / posture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)手勢/姿勢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit at my desk to work</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)坐下工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persistent ache</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)持續性疼痛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scrape user content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)大量下載網路資源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)損害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unauthorized exploitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)未經許可迫害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>automation / routine tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UC)自動化/單調任務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personal privacy = digital right = portrait right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(C)肖像權</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UC)訊號中斷；擾亂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breach = violate = compromise = undermine = exploit = erode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4563,7 +5182,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4636,6 +5255,12 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5002,7 +5627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
@@ -5161,139 +5786,158 @@
     </row>
     <row r="22" spans="1:3" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75">
       <c r="A24" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75">
       <c r="A26" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75">
       <c r="A27" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75">
       <c r="A28" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75">
       <c r="A30" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75">
       <c r="A32" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75">
       <c r="A34" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75">
       <c r="A36" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75">
       <c r="A37" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75">
       <c r="A38" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75">
       <c r="A39" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75">
       <c r="A40" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75">
+      <c r="A42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75">
+      <c r="A43" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5307,7 +5951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
@@ -5426,7 +6070,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>60</v>
@@ -5627,7 +6271,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s">
         <v>111</v>
@@ -5716,221 +6360,364 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B54" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B56" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B58" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B61" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B64" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B65" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" t="s">
         <v>334</v>
       </c>
-      <c r="B64" t="s">
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="2" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="2" t="s">
+      <c r="B67" t="s">
         <v>336</v>
       </c>
-      <c r="B65" t="s">
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="2" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="2" t="s">
+      <c r="B68" t="s">
         <v>338</v>
       </c>
-      <c r="B66" t="s">
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="2" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="2" t="s">
+      <c r="B69" t="s">
         <v>340</v>
       </c>
-      <c r="B67" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B68" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B69" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B71" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B72" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B73" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B75" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B76" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B77" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B78" t="s">
+        <v>480</v>
+      </c>
+      <c r="C78" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B79" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B80" t="s">
-        <v>423</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B81" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B82" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="B83" t="s">
-        <v>450</v>
-      </c>
-      <c r="C83" t="s">
-        <v>451</v>
+        <v>443</v>
+      </c>
+      <c r="C82" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B84" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B85" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B87" t="s">
+        <v>516</v>
+      </c>
+      <c r="C87" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B88" t="s">
+        <v>491</v>
+      </c>
+      <c r="C88" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B89" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B90" t="s">
+        <v>497</v>
+      </c>
+      <c r="C90" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B92" t="s">
+        <v>519</v>
+      </c>
+      <c r="C92" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B93" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B94" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B95" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B96" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B98" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B99" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B100" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B101" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B102" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B103" t="s">
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +6728,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EDC9FC-1DB6-4BC4-96F7-C5677C1DF68D}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="41.375" customWidth="1"/>
@@ -5961,7 +6748,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>71</v>
@@ -5983,7 +6770,7 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5994,7 +6781,7 @@
         <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6005,74 +6792,82 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B13" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B16" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B17" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B18" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6083,7 +6878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
@@ -6152,7 +6947,7 @@
     </row>
     <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>146</v>
@@ -6211,7 +7006,7 @@
     </row>
     <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>159</v>
@@ -6249,37 +7044,37 @@
     </row>
     <row r="21" spans="1:3" ht="16.5">
       <c r="A21" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.5">
       <c r="A22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5">
       <c r="A24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6287,96 +7082,96 @@
     </row>
     <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="2" t="s">
-        <v>173</v>
+        <v>476</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16.5">
       <c r="A27" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16.5">
       <c r="A28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16.5">
       <c r="A29" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.5">
       <c r="A30" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16.5">
       <c r="A32" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16.5">
       <c r="A34" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16.5">
       <c r="A35" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16.5">
       <c r="A36" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6384,53 +7179,53 @@
     </row>
     <row r="38" spans="1:3" ht="16.5">
       <c r="A38" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
       <c r="A39" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16.5">
       <c r="A40" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.5">
       <c r="A41" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
       <c r="A42" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16.5">
       <c r="A43" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6438,549 +7233,670 @@
     </row>
     <row r="45" spans="1:3" ht="16.5">
       <c r="A45" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16.5">
       <c r="A46" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16.5">
       <c r="A47" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16.5">
       <c r="A48" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.5">
       <c r="A49" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16.5">
       <c r="A50" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16.5">
       <c r="A52" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16.5">
       <c r="A53" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16.5">
       <c r="A54" s="2" t="s">
-        <v>195</v>
+        <v>473</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16.5">
       <c r="A55" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16.5">
       <c r="A56" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16.5">
       <c r="A57" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.5">
       <c r="A58" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16.5">
       <c r="A59" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16.5">
       <c r="A60" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16.5">
       <c r="A65" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="16.5">
       <c r="A66" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.75">
       <c r="A68" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.75">
       <c r="A69" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.75">
       <c r="A70" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.75">
       <c r="A71" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.75">
       <c r="A72" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15.75">
       <c r="A74" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15.75">
       <c r="A75" s="1" t="s">
-        <v>312</v>
+        <v>459</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75">
       <c r="A76" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75">
       <c r="A77" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.75">
       <c r="A78" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.75">
       <c r="A79" s="1" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.75">
       <c r="A80" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75">
       <c r="A82" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75">
       <c r="A83" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5">
       <c r="A84" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75">
       <c r="A85" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75">
       <c r="A86" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75">
       <c r="A87" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75">
       <c r="A88" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75">
       <c r="A89" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75">
       <c r="A90" s="1" t="s">
-        <v>383</v>
+        <v>458</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75">
       <c r="A91" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75">
       <c r="A92" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75">
       <c r="A94" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75">
       <c r="A95" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75">
       <c r="A96" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75">
       <c r="A97" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75">
       <c r="A98" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75">
       <c r="A99" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75">
       <c r="A100" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75">
       <c r="A101" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75">
       <c r="A102" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75">
       <c r="A104" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75">
       <c r="A105" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75">
       <c r="A106" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75">
       <c r="A107" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75">
       <c r="A108" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="16.5">
       <c r="A109" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75">
       <c r="A110" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75">
       <c r="A112" s="1" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75">
       <c r="A113" s="1" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="15.75">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="16.5">
       <c r="A114" s="1" t="s">
-        <v>458</v>
+        <v>98</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75">
       <c r="A115" s="1" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75">
       <c r="A116" s="1" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75">
       <c r="A117" s="1" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>466</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="15.75">
+      <c r="A118" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15.75">
+      <c r="A119" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="15.75">
+      <c r="A121" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="15.75">
+      <c r="A122" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="16.5">
+      <c r="A123" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="15.75">
+      <c r="A124" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="15.75">
+      <c r="A125" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="15.75">
+      <c r="A127" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="15.75">
+      <c r="A128" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="15.75">
+      <c r="A129" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15.75">
+      <c r="A130" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="15.75">
+      <c r="A131" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15.75">
+      <c r="A132" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="15.75">
+      <c r="A133" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60B7AA-CD24-493F-997A-CC594F03F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB682263-9B1A-4C8A-8CF0-F68C1EFF04CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
-    <sheet name="email" sheetId="2" r:id="rId2"/>
-    <sheet name="有禮貌專區" sheetId="5" r:id="rId3"/>
-    <sheet name="academic" sheetId="4" r:id="rId4"/>
+    <sheet name="Repeat" sheetId="7" r:id="rId2"/>
+    <sheet name="email" sheetId="2" r:id="rId3"/>
+    <sheet name="有禮貌專區" sheetId="5" r:id="rId4"/>
+    <sheet name="academic" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="586">
   <si>
     <t>Word</t>
   </si>
@@ -2653,10 +2654,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>company = firm = organization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>competent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3951,10 +3948,6 @@
       </rPr>
       <t>基本要求</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rival</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5175,6 +5168,432 @@
   </si>
   <si>
     <t>breach = violate = compromise = undermine = exploit = erode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canonical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>經典的；基督教教規的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name badge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>識別牌</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auditorium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>觀眾席；聽眾席</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># in the auditorium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakout room</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>討論室</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>at the desk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(prep)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>在…服務台</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>be finished using them</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>用完了</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>popular / famous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>受人歡迎的/知名的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>景點、服務通常強調受人歡迎</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exotic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>奇異的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guided tour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>導覽</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innovation / innovative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>兩個字數相同</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(UC)/(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>創新</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>company = firm = organization = corporation = enterprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rival = competitor = counterpart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XX do not automatically compromise XX; on the contrary,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)XX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>不必然造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>XX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>相反的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attract capital investment to research</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>吸引研究資金</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineer = design</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>研發</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>更好的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scale = grow = expand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>成長</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disrupt planned program</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)影響原定計畫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double-check the order details</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vi)仔細檢查訂單內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>one day prior to delivery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adv)送貨前一天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(vt)把sth給sb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>provide sth for sb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clear and concise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>言簡意賅的</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>壯舉</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5627,7 +6046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
@@ -5794,150 +6213,177 @@
     </row>
     <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75">
       <c r="A24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75">
       <c r="A26" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75">
       <c r="A27" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75">
       <c r="A28" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75">
       <c r="A30" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75">
       <c r="A32" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75">
       <c r="A34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75">
       <c r="A36" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75">
       <c r="A37" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75">
       <c r="A38" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75">
       <c r="A39" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75">
       <c r="A40" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75">
       <c r="A42" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75">
       <c r="A43" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>490</v>
+    </row>
+    <row r="44" spans="1:3" ht="15.75">
+      <c r="A44" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75">
+      <c r="A46" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75">
+      <c r="A47" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -5950,8 +6396,106 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD70CE19-39FC-4A75-8490-A3E34FB5A0D1}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75">
+      <c r="A2" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
+      <c r="A3" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75">
+      <c r="A4" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75">
+      <c r="A5" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75">
+      <c r="A6" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75">
+      <c r="A7" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75">
+      <c r="A8" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75">
+      <c r="A9" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C9715-F76A-4BF6-9ACA-C6429A27B6E2}">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
@@ -6070,7 +6614,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>60</v>
@@ -6271,7 +6815,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s">
         <v>111</v>
@@ -6408,316 +6952,348 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B58" t="s">
         <v>289</v>
-      </c>
-      <c r="B58" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B59" t="s">
         <v>287</v>
-      </c>
-      <c r="B59" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B60" t="s">
         <v>293</v>
-      </c>
-      <c r="B60" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" t="s">
         <v>295</v>
-      </c>
-      <c r="B61" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B62" t="s">
         <v>297</v>
-      </c>
-      <c r="B62" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B64" t="s">
         <v>329</v>
-      </c>
-      <c r="B64" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B65" t="s">
         <v>331</v>
-      </c>
-      <c r="B65" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B66" t="s">
         <v>333</v>
-      </c>
-      <c r="B66" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B67" t="s">
         <v>335</v>
-      </c>
-      <c r="B67" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B68" t="s">
         <v>337</v>
-      </c>
-      <c r="B68" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B69" t="s">
         <v>339</v>
-      </c>
-      <c r="B69" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B71" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B72" t="s">
         <v>355</v>
-      </c>
-      <c r="B72" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B73" t="s">
         <v>357</v>
-      </c>
-      <c r="B73" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B75" t="s">
         <v>385</v>
-      </c>
-      <c r="B75" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B76" t="s">
         <v>387</v>
-      </c>
-      <c r="B76" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B78" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C78" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B79" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B81" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B82" t="s">
+        <v>441</v>
+      </c>
+      <c r="C82" t="s">
         <v>442</v>
-      </c>
-      <c r="B82" t="s">
-        <v>443</v>
-      </c>
-      <c r="C82" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B87" t="s">
+        <v>514</v>
+      </c>
+      <c r="C87" t="s">
         <v>515</v>
-      </c>
-      <c r="B87" t="s">
-        <v>516</v>
-      </c>
-      <c r="C87" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B88" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C88" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B90" t="s">
+        <v>495</v>
+      </c>
+      <c r="C90" t="s">
         <v>496</v>
-      </c>
-      <c r="B90" t="s">
-        <v>497</v>
-      </c>
-      <c r="C90" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C92" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B93" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B94" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B95" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B96" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B99" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B100" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B103" t="s">
-        <v>539</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B105" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B106" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B107" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B108" t="s">
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -6726,7 +7302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EDC9FC-1DB6-4BC4-96F7-C5677C1DF68D}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -6748,7 +7324,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>71</v>
@@ -6770,7 +7346,7 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6781,7 +7357,7 @@
         <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6792,7 +7368,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6813,61 +7389,61 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" t="s">
         <v>283</v>
-      </c>
-      <c r="B12" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" t="s">
         <v>285</v>
-      </c>
-      <c r="B13" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" t="s">
         <v>291</v>
-      </c>
-      <c r="B14" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" t="s">
         <v>350</v>
-      </c>
-      <c r="B16" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" t="s">
         <v>352</v>
-      </c>
-      <c r="B17" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" t="s">
+        <v>417</v>
+      </c>
+      <c r="C18" t="s">
         <v>418</v>
-      </c>
-      <c r="B18" t="s">
-        <v>419</v>
-      </c>
-      <c r="C18" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B20" t="s">
         <v>383</v>
-      </c>
-      <c r="B20" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6876,9 +7452,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.75" style="1" customWidth="1"/>
@@ -6947,7 +7523,7 @@
     </row>
     <row r="8" spans="1:3" ht="16.5">
       <c r="A8" s="2" t="s">
-        <v>277</v>
+        <v>563</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>146</v>
@@ -7044,7 +7620,7 @@
     </row>
     <row r="21" spans="1:3" ht="16.5">
       <c r="A21" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>167</v>
@@ -7082,7 +7658,7 @@
     </row>
     <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>197</v>
@@ -7144,7 +7720,7 @@
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>225</v>
@@ -7273,7 +7849,7 @@
     </row>
     <row r="50" spans="1:3" ht="16.5">
       <c r="A50" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>219</v>
@@ -7297,7 +7873,7 @@
     </row>
     <row r="54" spans="1:3" ht="16.5">
       <c r="A54" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>221</v>
@@ -7431,472 +8007,520 @@
     </row>
     <row r="72" spans="1:2" ht="15.75">
       <c r="A72" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15.75">
       <c r="A74" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15.75">
       <c r="A75" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75">
       <c r="A76" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75">
       <c r="A77" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.75">
       <c r="A78" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.75">
       <c r="A79" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.75">
       <c r="A80" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="15.75">
+    </row>
+    <row r="82" spans="1:2" ht="15.75">
       <c r="A82" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="15.75">
+    </row>
+    <row r="83" spans="1:2" ht="15.75">
       <c r="A83" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B83" s="1" t="s">
+    </row>
+    <row r="84" spans="1:2" ht="16.5">
+      <c r="A84" s="1" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="16.5">
-      <c r="A84" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B84" s="1" t="s">
+    </row>
+    <row r="85" spans="1:2" ht="15.75">
+      <c r="A85" s="1" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="15.75">
-      <c r="A85" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:2" ht="15.75">
+      <c r="A86" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="15.75">
-      <c r="A86" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B86" s="1" t="s">
+    </row>
+    <row r="88" spans="1:2" ht="15.75">
+      <c r="A88" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75">
+      <c r="A89" s="1" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="15.75">
-      <c r="A87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B87" s="1" t="s">
+    </row>
+    <row r="90" spans="1:2" ht="15.75">
+      <c r="A90" s="1" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="15.75">
-      <c r="A88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B88" s="1" t="s">
+    </row>
+    <row r="91" spans="1:2" ht="15.75">
+      <c r="A91" s="1" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="15.75">
-      <c r="A89" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="15.75">
-      <c r="A90" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="15.75">
-      <c r="A91" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="15.75">
+    </row>
+    <row r="92" spans="1:2" ht="15.75">
       <c r="A92" s="1" t="s">
-        <v>376</v>
+        <v>456</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75">
+    <row r="93" spans="1:2" ht="15.75">
+      <c r="A93" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15.75">
       <c r="A94" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.75">
+      <c r="A96" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="15.75">
-      <c r="A95" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="15.75">
-      <c r="A96" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75">
       <c r="A97" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75">
       <c r="A98" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75">
       <c r="A99" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75">
       <c r="A100" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75">
       <c r="A101" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75">
       <c r="A102" s="1" t="s">
-        <v>408</v>
+        <v>564</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15.75">
+      <c r="A103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75">
       <c r="A104" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.75">
-      <c r="A105" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75">
       <c r="A106" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75">
       <c r="A107" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75">
       <c r="A108" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="16.5">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15.75">
       <c r="A109" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75">
       <c r="A110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="16.5">
+      <c r="A111" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75">
       <c r="A112" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15.75">
+      <c r="A114" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.75">
-      <c r="A113" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="16.5">
-      <c r="A114" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75">
       <c r="A115" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="15.75">
+        <v>448</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="16.5">
       <c r="A116" s="1" t="s">
-        <v>454</v>
+        <v>98</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75">
       <c r="A117" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75">
       <c r="A118" s="1" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75">
       <c r="A119" s="1" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>464</v>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15.75">
+      <c r="A120" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75">
       <c r="A121" s="1" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="15.75">
-      <c r="A122" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="16.5">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="15.75">
       <c r="A123" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75">
       <c r="A124" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="15.75">
+        <v>466</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="16.5">
       <c r="A125" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="15.75">
+      <c r="A126" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75">
       <c r="A127" s="1" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="15.75">
-      <c r="A128" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75">
       <c r="A129" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75">
       <c r="A130" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75">
       <c r="A131" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75">
       <c r="A132" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75">
       <c r="A133" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="15.75">
+      <c r="A134" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="15.75">
+      <c r="A135" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="16.5">
+      <c r="A137" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15.75">
+      <c r="A138" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="15.75">
+      <c r="A139" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="15.75">
+      <c r="A140" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="15.75">
+      <c r="A141" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
   </sheetData>

--- a/TestAdmit.xlsx
+++ b/TestAdmit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\作業\英文\單字卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF1D529-D983-41F5-9BC7-09B55F30949A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADD5F11-E9F0-4B1D-9902-8FC84BAF00F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="閱讀紀錄" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="904">
   <si>
     <t>Word</t>
   </si>
@@ -3337,39 +3337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>比</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>only, just</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>好多了</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>baseline expectation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7495,10 +7462,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inspire profound collective introspection = societal reconsideration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A serves as an indispensable vehicle to</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8365,6 +8328,197 @@
   </si>
   <si>
     <t>(idiom)喜歡/感謝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightning rig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>打光</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credentials</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(plural)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>用戶登錄資料</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>課堂資訊主頁</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fund community training programs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>贊助地方訓練計畫</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>displace certain routine tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(vi)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>取代低技術力工作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrial transformation creates high-valued positions in research and innovation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(idiom)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>產業轉型：研發</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>正向用語</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merely = solely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>負面用語</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inevitably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(adv)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>不可避地</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>educational campaign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>教育活動</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspire collective active = societal reconsideration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9059,262 +9213,262 @@
     </row>
     <row r="33" spans="1:3" ht="15.6">
       <c r="A33" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.6">
       <c r="A34" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.6">
       <c r="A36" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.6">
       <c r="A37" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.6">
       <c r="A38" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.6">
       <c r="A40" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.6">
       <c r="A41" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.6">
       <c r="A42" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="C42" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.6">
       <c r="A44" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.6">
       <c r="A45" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.6">
       <c r="A47" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.6">
       <c r="A48" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15.6">
       <c r="A49" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.6">
       <c r="A50" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>631</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.6">
       <c r="A52" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.6">
       <c r="A53" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15.6">
       <c r="A54" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.6">
       <c r="A56" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15.6">
       <c r="A57" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15.6">
       <c r="A58" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="15.6">
       <c r="A60" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15.6">
       <c r="A61" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15.6">
       <c r="A62" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15.6">
       <c r="A63" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.6">
       <c r="A65" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.6">
       <c r="A66" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15.6">
       <c r="A67" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.6">
       <c r="A72" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -9328,7 +9482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD70CE19-39FC-4A75-8490-A3E34FB5A0D1}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
@@ -9350,246 +9504,270 @@
     </row>
     <row r="2" spans="1:3" ht="15.6">
       <c r="A2" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6">
       <c r="A3" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6">
       <c r="A4" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6">
       <c r="A5" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6">
       <c r="A6" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6">
       <c r="A7" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6">
       <c r="A8" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6">
       <c r="A10" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6">
       <c r="A11" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6">
       <c r="A12" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6">
       <c r="A13" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.6">
       <c r="A14" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6">
       <c r="A15" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.6">
       <c r="A17" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.6">
       <c r="A18" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.6">
       <c r="A19" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.6">
       <c r="A20" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.6">
       <c r="A22" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.6">
       <c r="A23" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.6">
       <c r="A24" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.6">
       <c r="A33" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16.2">
       <c r="A34" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.6">
       <c r="A35" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.6">
+      <c r="A37" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.6">
+      <c r="A38" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.6">
+      <c r="A39" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -9882,10 +10060,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B33" t="s">
         <v>734</v>
-      </c>
-      <c r="B33" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -10033,7 +10211,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B54" t="s">
         <v>232</v>
@@ -10132,7 +10310,7 @@
         <v>296</v>
       </c>
       <c r="B68" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -10145,10 +10323,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B71" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -10185,244 +10363,244 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B78" t="s">
+        <v>411</v>
+      </c>
+      <c r="C78" t="s">
         <v>412</v>
-      </c>
-      <c r="C78" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B79" t="s">
         <v>362</v>
-      </c>
-      <c r="B79" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B81" t="s">
         <v>379</v>
-      </c>
-      <c r="B81" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" t="s">
         <v>381</v>
       </c>
-      <c r="B82" t="s">
-        <v>382</v>
-      </c>
       <c r="C82" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B85" t="s">
         <v>414</v>
-      </c>
-      <c r="B85" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B86" t="s">
         <v>416</v>
-      </c>
-      <c r="B86" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B88" t="s">
         <v>447</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>448</v>
-      </c>
-      <c r="C88" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B89" t="s">
+        <v>422</v>
+      </c>
+      <c r="C89" t="s">
         <v>423</v>
-      </c>
-      <c r="C89" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B90" t="s">
         <v>426</v>
-      </c>
-      <c r="B90" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B91" t="s">
         <v>428</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>429</v>
-      </c>
-      <c r="C91" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B93" t="s">
         <v>450</v>
       </c>
-      <c r="B93" t="s">
-        <v>451</v>
-      </c>
       <c r="C93" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B94" t="s">
         <v>452</v>
-      </c>
-      <c r="B94" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B95" t="s">
         <v>455</v>
-      </c>
-      <c r="B95" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B96" t="s">
         <v>457</v>
-      </c>
-      <c r="B96" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B97" t="s">
         <v>459</v>
-      </c>
-      <c r="B97" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B99" t="s">
         <v>461</v>
-      </c>
-      <c r="B99" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B100" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B101" t="s">
         <v>464</v>
-      </c>
-      <c r="B101" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B102" t="s">
         <v>466</v>
-      </c>
-      <c r="B102" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B103" t="s">
         <v>468</v>
-      </c>
-      <c r="B103" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B104" t="s">
         <v>470</v>
-      </c>
-      <c r="B104" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B106" t="s">
         <v>504</v>
-      </c>
-      <c r="B106" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B107" t="s">
         <v>506</v>
-      </c>
-      <c r="B107" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B108" t="s">
         <v>508</v>
-      </c>
-      <c r="B108" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B109" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B111" t="s">
         <v>531</v>
-      </c>
-      <c r="B111" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B112" t="s">
         <v>533</v>
-      </c>
-      <c r="B112" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -10430,149 +10608,149 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B114" t="s">
         <v>637</v>
-      </c>
-      <c r="B114" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B115" t="s">
         <v>639</v>
-      </c>
-      <c r="B115" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B116" t="s">
         <v>641</v>
-      </c>
-      <c r="B116" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B117" t="s">
         <v>643</v>
-      </c>
-      <c r="B117" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B118" t="s">
         <v>645</v>
-      </c>
-      <c r="B118" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B120" t="s">
         <v>671</v>
-      </c>
-      <c r="B120" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B121" t="s">
         <v>683</v>
-      </c>
-      <c r="B121" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B122" t="s">
         <v>673</v>
-      </c>
-      <c r="B122" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B123" t="s">
         <v>675</v>
-      </c>
-      <c r="B123" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B124" t="s">
         <v>681</v>
-      </c>
-      <c r="B124" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B126" t="s">
         <v>736</v>
-      </c>
-      <c r="B126" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B127" t="s">
         <v>738</v>
-      </c>
-      <c r="B127" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B129" t="s">
+        <v>808</v>
+      </c>
+      <c r="C129" t="s">
         <v>809</v>
-      </c>
-      <c r="B129" t="s">
-        <v>810</v>
-      </c>
-      <c r="C129" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B130" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B131" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B132" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B133" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B134" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -10603,7 +10781,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>71</v>
@@ -10625,7 +10803,7 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10636,7 +10814,7 @@
         <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10647,7 +10825,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -10708,13 +10886,13 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" t="s">
         <v>365</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>366</v>
-      </c>
-      <c r="C18" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -10727,13 +10905,13 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B21" t="s">
         <v>535</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>536</v>
-      </c>
-      <c r="C21" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -10741,45 +10919,45 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B23" t="s">
+        <v>646</v>
+      </c>
+      <c r="C23" t="s">
         <v>647</v>
-      </c>
-      <c r="C23" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B24" t="s">
         <v>650</v>
-      </c>
-      <c r="B24" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B26" t="s">
         <v>677</v>
-      </c>
-      <c r="B26" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B27" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B29" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>
@@ -10790,7 +10968,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835CE181-6036-435B-99AC-0DA4E148DEFD}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -10874,10 +11052,10 @@
     </row>
     <row r="14" spans="1:3" ht="15.6">
       <c r="A14" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6">
@@ -10890,7 +11068,7 @@
     </row>
     <row r="16" spans="1:3" ht="15.6">
       <c r="A16" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>331</v>
@@ -10922,96 +11100,88 @@
     </row>
     <row r="22" spans="1:3" ht="15.6">
       <c r="A22" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.6">
       <c r="A23" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.6">
       <c r="A24" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.6">
       <c r="A25" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.6">
       <c r="A26" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.6">
       <c r="A31" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>656</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.6">
-      <c r="A34" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -11022,7 +11192,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A775B5-E4A7-475C-821D-92B77986C411}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -11051,7 +11221,7 @@
     </row>
     <row r="3" spans="1:4" ht="16.2">
       <c r="A3" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>139</v>
@@ -11059,42 +11229,42 @@
     </row>
     <row r="4" spans="1:4" ht="15.6">
       <c r="A4" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="15.6">
       <c r="A5" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="15.6">
       <c r="A6" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="15.6">
       <c r="A7" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.2">
       <c r="A8" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>200</v>
@@ -11102,18 +11272,18 @@
     </row>
     <row r="9" spans="1:4" ht="15.6">
       <c r="A9" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6">
       <c r="A10" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.2">
@@ -11126,10 +11296,10 @@
     </row>
     <row r="13" spans="1:4" ht="16.2">
       <c r="A13" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6">
@@ -11140,278 +11310,297 @@
         <v>352</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="16.2">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
       <c r="A15" s="1" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>700</v>
+        <v>898</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.2">
       <c r="A16" s="1" t="s">
-        <v>403</v>
+        <v>877</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6">
+    <row r="17" spans="1:3" ht="16.2">
       <c r="A17" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.6">
       <c r="A18" s="1" t="s">
-        <v>439</v>
+        <v>697</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>440</v>
+        <v>700</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.6">
       <c r="A19" s="1" t="s">
-        <v>776</v>
+        <v>899</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>615</v>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.6">
+      <c r="A20" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.6">
       <c r="A21" s="1" t="s">
-        <v>242</v>
+        <v>775</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.6">
-      <c r="A22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>552</v>
+        <v>614</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.6">
       <c r="A23" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.6">
+      <c r="A24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.6">
+      <c r="A25" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.6">
-      <c r="A24" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.6">
       <c r="A26" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.6">
+      <c r="A28" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.2">
-      <c r="A27" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="1:3" ht="16.2">
+      <c r="A29" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="16.2">
-      <c r="A28" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="16.2">
-      <c r="A29" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.2">
       <c r="A30" s="1" t="s">
-        <v>588</v>
+        <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.2">
+      <c r="A31" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16.2">
+      <c r="A32" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6">
-      <c r="A32" s="1" t="s">
+    <row r="34" spans="1:3" ht="15.6">
+      <c r="A34" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6">
-      <c r="A33" s="1" t="s">
+    <row r="35" spans="1:3" ht="15.6">
+      <c r="A35" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.2">
-      <c r="A34" s="1" t="s">
+    <row r="36" spans="1:3" ht="16.2">
+      <c r="A36" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.2">
-      <c r="A35" s="1" t="s">
+    </row>
+    <row r="37" spans="1:3" ht="16.2">
+      <c r="A37" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.6">
-      <c r="A37" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.6">
-      <c r="A38" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.6">
       <c r="A39" s="1" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.6">
       <c r="A40" s="1" t="s">
-        <v>591</v>
+        <v>323</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>392</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.6">
       <c r="A41" s="1" t="s">
-        <v>740</v>
+        <v>346</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>530</v>
+        <v>347</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>741</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.6">
       <c r="A42" s="1" t="s">
-        <v>763</v>
+        <v>590</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>764</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.6">
+      <c r="A43" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.6">
       <c r="A44" s="1" t="s">
-        <v>441</v>
+        <v>762</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.6">
-      <c r="A45" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.6">
       <c r="A46" s="1" t="s">
-        <v>832</v>
+        <v>440</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>833</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.6">
+      <c r="A47" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.6">
       <c r="A48" s="1" t="s">
-        <v>749</v>
+        <v>830</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.6">
-      <c r="A49" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.6">
       <c r="A50" s="1" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.6">
       <c r="A51" s="1" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.6">
       <c r="A52" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.6">
+      <c r="A53" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.6">
+      <c r="A54" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -11422,7 +11611,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39537F9-A320-4961-952C-ED54FA95C1D4}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -11443,10 +11632,10 @@
     </row>
     <row r="2" spans="1:3" ht="15.6">
       <c r="A2" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6">
@@ -11454,7 +11643,7 @@
         <v>136</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6">
@@ -11462,7 +11651,7 @@
         <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6">
@@ -11470,7 +11659,7 @@
         <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6">
@@ -11478,7 +11667,7 @@
         <v>146</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11489,26 +11678,26 @@
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6">
       <c r="A9" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6">
       <c r="A10" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6">
@@ -11516,7 +11705,7 @@
         <v>161</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6">
@@ -11524,7 +11713,7 @@
         <v>162</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6">
@@ -11532,7 +11721,7 @@
         <v>163</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6">
@@ -11540,31 +11729,31 @@
         <v>217</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.6">
       <c r="A16" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.6">
       <c r="A17" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.6">
       <c r="A19" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.6">
@@ -11572,357 +11761,381 @@
         <v>349</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.6">
       <c r="A21" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.6">
       <c r="A34" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.6">
       <c r="A35" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.6">
       <c r="A36" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.6">
       <c r="A37" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.6">
       <c r="A39" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.6">
       <c r="A40" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.6">
       <c r="A41" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.6">
       <c r="A42" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.6">
       <c r="A43" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.6">
       <c r="A44" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.6">
       <c r="A45" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.6">
       <c r="A46" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.6">
       <c r="A47" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15.6">
       <c r="A49" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.6">
       <c r="A50" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.6">
       <c r="A51" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.6">
       <c r="A52" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>726</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.6">
       <c r="A53" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.6">
       <c r="A55" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.6">
       <c r="A56" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15.6">
       <c r="A57" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15.6">
       <c r="A58" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15.6">
       <c r="A59" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="15.6">
       <c r="A60" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15.6">
       <c r="A61" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15.6">
       <c r="A62" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15.6">
       <c r="A64" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.6">
       <c r="A65" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.6">
       <c r="A66" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15.6">
       <c r="A67" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.6">
+      <c r="A71" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.6">
+      <c r="A72" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.6">
+      <c r="A73" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -11973,7 +12186,7 @@
     </row>
     <row r="5" spans="1:3" ht="16.2">
       <c r="A5" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>178</v>
@@ -12091,7 +12304,7 @@
     </row>
     <row r="23" spans="1:3" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>273</v>
@@ -12131,80 +12344,80 @@
     </row>
     <row r="29" spans="1:3" ht="15.6">
       <c r="A29" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.6">
       <c r="A33" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.6">
       <c r="A35" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.6">
       <c r="A36" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.6">
       <c r="A37" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.6">
       <c r="A38" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -12212,110 +12425,110 @@
     </row>
     <row r="40" spans="1:3" ht="15.6">
       <c r="A40" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.6">
       <c r="A41" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.6">
       <c r="A42" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.6">
       <c r="A43" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.6">
       <c r="A44" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.6">
       <c r="A45" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.6">
       <c r="A47" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="C47" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.6">
       <c r="A48" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.6">
       <c r="A49" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.6">
       <c r="A50" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.6">
       <c r="A51" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.6">
       <c r="A52" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -12326,7 +12539,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06ECD2A-C945-4C7A-90CC-1D0BA80BFE9A}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.77734375" style="1" customWidth="1"/>
@@ -12503,15 +12716,15 @@
     </row>
     <row r="24" spans="1:3" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.6">
       <c r="A25" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>320</v>
@@ -12530,135 +12743,151 @@
         <v>286</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6">
       <c r="A30" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>685</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.6">
       <c r="A33" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.6">
       <c r="A34" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.6">
       <c r="A35" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.6">
       <c r="A37" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.6">
       <c r="A38" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.6">
       <c r="A39" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.6">
       <c r="A40" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.6">
       <c r="A41" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.6">
+      <c r="A42" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.6">
-      <c r="A43" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.6">
       <c r="A44" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>785</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.6">
       <c r="A45" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.6">
       <c r="A46" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.6">
       <c r="A47" s="1" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.6">
+      <c r="A48" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.6">
+      <c r="A49" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>789</v>
       </c>
     </row>
   </sheetData>
